--- a/storage/assets/list_kpb/kpb_so_08_2025/fisik/SO BK 17.09.2025.xlsx
+++ b/storage/assets/list_kpb/kpb_so_08_2025/fisik/SO BK 17.09.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BACKUP DESKTOP MEI (24.09.2025)\VALIDASI KPB SO\KPB cek di bulan Sept 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willi\Project\cek-gambar-astras\storage\assets\list_kpb\kpb_so_08_2025\fisik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6971EAE-298D-4A5C-8803-B99FC4247338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA82A8B1-32B1-43BD-8FAF-46448D573224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="12804-250902_1049" sheetId="2" r:id="rId1"/>
@@ -3167,16 +3167,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F937"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" customWidth="1"/>
+    <col min="3" max="4" width="11.33203125" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="F1" s="7"/>
     </row>
-    <row r="2" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="F2" s="8"/>
     </row>
-    <row r="3" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>27</v>
       </c>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>29</v>
       </c>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>32</v>
       </c>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>34</v>
       </c>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>37</v>
       </c>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>39</v>
       </c>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>43</v>
       </c>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>44</v>
       </c>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>46</v>
       </c>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>47</v>
       </c>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>49</v>
       </c>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>51</v>
       </c>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>52</v>
       </c>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>53</v>
       </c>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>54</v>
       </c>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>55</v>
       </c>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>57</v>
       </c>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>59</v>
       </c>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>60</v>
       </c>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>61</v>
       </c>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>62</v>
       </c>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>64</v>
       </c>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>65</v>
       </c>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>67</v>
       </c>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>69</v>
       </c>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>71</v>
       </c>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>72</v>
       </c>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>73</v>
       </c>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="F40" s="8"/>
     </row>
-    <row r="41" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>75</v>
       </c>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="F41" s="8"/>
     </row>
-    <row r="42" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>78</v>
       </c>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="F42" s="8"/>
     </row>
-    <row r="43" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>80</v>
       </c>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F43" s="8"/>
     </row>
-    <row r="44" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>82</v>
       </c>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="F44" s="8"/>
     </row>
-    <row r="45" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>83</v>
       </c>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="F45" s="8"/>
     </row>
-    <row r="46" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>84</v>
       </c>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>85</v>
       </c>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>87</v>
       </c>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F48" s="8"/>
     </row>
-    <row r="49" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>89</v>
       </c>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>91</v>
       </c>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="F50" s="8"/>
     </row>
-    <row r="51" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>94</v>
       </c>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>95</v>
       </c>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="F52" s="8"/>
     </row>
-    <row r="53" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>98</v>
       </c>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="F53" s="8"/>
     </row>
-    <row r="54" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>100</v>
       </c>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F54" s="8"/>
     </row>
-    <row r="55" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>101</v>
       </c>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F55" s="8"/>
     </row>
-    <row r="56" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>102</v>
       </c>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>104</v>
       </c>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="F57" s="8"/>
     </row>
-    <row r="58" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>107</v>
       </c>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="F58" s="8"/>
     </row>
-    <row r="59" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>109</v>
       </c>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="F59" s="8"/>
     </row>
-    <row r="60" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>111</v>
       </c>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>113</v>
       </c>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F61" s="8"/>
     </row>
-    <row r="62" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>114</v>
       </c>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="F62" s="8"/>
     </row>
-    <row r="63" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>115</v>
       </c>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F63" s="8"/>
     </row>
-    <row r="64" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>116</v>
       </c>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="F64" s="8"/>
     </row>
-    <row r="65" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>118</v>
       </c>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F65" s="8"/>
     </row>
-    <row r="66" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>120</v>
       </c>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="F66" s="8"/>
     </row>
-    <row r="67" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>122</v>
       </c>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="F67" s="8"/>
     </row>
-    <row r="68" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>125</v>
       </c>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="F68" s="8"/>
     </row>
-    <row r="69" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>127</v>
       </c>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="F69" s="8"/>
     </row>
-    <row r="70" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>129</v>
       </c>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F70" s="8"/>
     </row>
-    <row r="71" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>130</v>
       </c>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="F71" s="8"/>
     </row>
-    <row r="72" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>132</v>
       </c>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="F72" s="8"/>
     </row>
-    <row r="73" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>133</v>
       </c>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="F73" s="8"/>
     </row>
-    <row r="74" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>135</v>
       </c>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="F74" s="8"/>
     </row>
-    <row r="75" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>41</v>
       </c>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="F75" s="8"/>
     </row>
-    <row r="76" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>37</v>
       </c>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="F76" s="8"/>
     </row>
-    <row r="77" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>34</v>
       </c>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F77" s="8"/>
     </row>
-    <row r="78" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>39</v>
       </c>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="F78" s="8"/>
     </row>
-    <row r="79" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>138</v>
       </c>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="F79" s="8"/>
     </row>
-    <row r="80" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>29</v>
       </c>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F80" s="8"/>
     </row>
-    <row r="81" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>140</v>
       </c>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F81" s="8"/>
     </row>
-    <row r="82" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>69</v>
       </c>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="F82" s="8"/>
     </row>
-    <row r="83" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>64</v>
       </c>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="F83" s="8"/>
     </row>
-    <row r="84" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>65</v>
       </c>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="F84" s="8"/>
     </row>
-    <row r="85" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>62</v>
       </c>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="F85" s="8"/>
     </row>
-    <row r="86" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>72</v>
       </c>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="F86" s="8"/>
     </row>
-    <row r="87" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>67</v>
       </c>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="F87" s="8"/>
     </row>
-    <row r="88" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>71</v>
       </c>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="F88" s="8"/>
     </row>
-    <row r="89" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>61</v>
       </c>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="F89" s="8"/>
     </row>
-    <row r="90" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>55</v>
       </c>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="F90" s="8"/>
     </row>
-    <row r="91" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>54</v>
       </c>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F91" s="8"/>
     </row>
-    <row r="92" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>60</v>
       </c>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="F92" s="8"/>
     </row>
-    <row r="93" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>142</v>
       </c>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="F93" s="8"/>
     </row>
-    <row r="94" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>19</v>
       </c>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="F94" s="8"/>
     </row>
-    <row r="95" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>144</v>
       </c>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="F95" s="8"/>
     </row>
-    <row r="96" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>145</v>
       </c>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="F96" s="8"/>
     </row>
-    <row r="97" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>147</v>
       </c>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="F97" s="8"/>
     </row>
-    <row r="98" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>148</v>
       </c>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F98" s="8"/>
     </row>
-    <row r="99" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>149</v>
       </c>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="F99" s="8"/>
     </row>
-    <row r="100" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>150</v>
       </c>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="F100" s="8"/>
     </row>
-    <row r="101" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>44</v>
       </c>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="F101" s="8"/>
     </row>
-    <row r="102" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>151</v>
       </c>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="F102" s="8"/>
     </row>
-    <row r="103" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>153</v>
       </c>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="F103" s="8"/>
     </row>
-    <row r="104" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>51</v>
       </c>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="F104" s="8"/>
     </row>
-    <row r="105" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>57</v>
       </c>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F105" s="8"/>
     </row>
-    <row r="106" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>46</v>
       </c>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F106" s="8"/>
     </row>
-    <row r="107" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>52</v>
       </c>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="F107" s="8"/>
     </row>
-    <row r="108" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>53</v>
       </c>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="F108" s="8"/>
     </row>
-    <row r="109" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>49</v>
       </c>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="F109" s="8"/>
     </row>
-    <row r="110" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>47</v>
       </c>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="F110" s="8"/>
     </row>
-    <row r="111" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>59</v>
       </c>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F111" s="8"/>
     </row>
-    <row r="112" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>154</v>
       </c>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="F112" s="8"/>
     </row>
-    <row r="113" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>156</v>
       </c>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="F113" s="8"/>
     </row>
-    <row r="114" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
         <v>157</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>158</v>
       </c>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="F115" s="8"/>
     </row>
-    <row r="116" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>159</v>
       </c>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="F116" s="8"/>
     </row>
-    <row r="117" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>160</v>
       </c>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="F117" s="8"/>
     </row>
-    <row r="118" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>162</v>
       </c>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="F118" s="8"/>
     </row>
-    <row r="119" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>163</v>
       </c>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="F119" s="8"/>
     </row>
-    <row r="120" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>164</v>
       </c>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="F120" s="8"/>
     </row>
-    <row r="121" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>166</v>
       </c>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="F121" s="8"/>
     </row>
-    <row r="122" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>168</v>
       </c>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F122" s="8"/>
     </row>
-    <row r="123" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>170</v>
       </c>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="F123" s="8"/>
     </row>
-    <row r="124" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>172</v>
       </c>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="F124" s="8"/>
     </row>
-    <row r="125" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>174</v>
       </c>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="F125" s="8"/>
     </row>
-    <row r="126" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>176</v>
       </c>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="F126" s="8"/>
     </row>
-    <row r="127" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>178</v>
       </c>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="F127" s="8"/>
     </row>
-    <row r="128" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>180</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>182</v>
       </c>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="F129" s="8"/>
     </row>
-    <row r="130" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>184</v>
       </c>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="F130" s="8"/>
     </row>
-    <row r="131" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>186</v>
       </c>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="F131" s="8"/>
     </row>
-    <row r="132" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>187</v>
       </c>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="F132" s="8"/>
     </row>
-    <row r="133" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>188</v>
       </c>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="F133" s="8"/>
     </row>
-    <row r="134" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>116</v>
       </c>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="F134" s="8"/>
     </row>
-    <row r="135" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>115</v>
       </c>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="F135" s="8"/>
     </row>
-    <row r="136" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>114</v>
       </c>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F136" s="8"/>
     </row>
-    <row r="137" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>190</v>
       </c>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="F137" s="8"/>
     </row>
-    <row r="138" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>192</v>
       </c>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="F138" s="8"/>
     </row>
-    <row r="139" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>118</v>
       </c>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="F139" s="8"/>
     </row>
-    <row r="140" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>133</v>
       </c>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="F140" s="8"/>
     </row>
-    <row r="141" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>132</v>
       </c>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="F141" s="8"/>
     </row>
-    <row r="142" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>195</v>
       </c>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="F142" s="8"/>
     </row>
-    <row r="143" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>197</v>
       </c>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="F143" s="8"/>
     </row>
-    <row r="144" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>199</v>
       </c>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="F144" s="8"/>
     </row>
-    <row r="145" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>201</v>
       </c>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="F145" s="8"/>
     </row>
-    <row r="146" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>135</v>
       </c>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F146" s="8"/>
     </row>
-    <row r="147" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>203</v>
       </c>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="F147" s="8"/>
     </row>
-    <row r="148" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>205</v>
       </c>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="F148" s="8"/>
     </row>
-    <row r="149" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>206</v>
       </c>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="F149" s="8"/>
     </row>
-    <row r="150" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>208</v>
       </c>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="F150" s="8"/>
     </row>
-    <row r="151" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>209</v>
       </c>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="F151" s="8"/>
     </row>
-    <row r="152" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>210</v>
       </c>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="F152" s="8"/>
     </row>
-    <row r="153" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>212</v>
       </c>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="F153" s="8"/>
     </row>
-    <row r="154" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>213</v>
       </c>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="F154" s="8"/>
     </row>
-    <row r="155" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>214</v>
       </c>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="F155" s="8"/>
     </row>
-    <row r="156" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>216</v>
       </c>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F156" s="8"/>
     </row>
-    <row r="157" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>218</v>
       </c>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="F157" s="8"/>
     </row>
-    <row r="158" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>219</v>
       </c>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="F158" s="8"/>
     </row>
-    <row r="159" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>220</v>
       </c>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="F159" s="8"/>
     </row>
-    <row r="160" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>221</v>
       </c>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="F160" s="8"/>
     </row>
-    <row r="161" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>163</v>
       </c>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="F161" s="8"/>
     </row>
-    <row r="162" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>168</v>
       </c>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="F162" s="8"/>
     </row>
-    <row r="163" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>164</v>
       </c>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="F163" s="8"/>
     </row>
-    <row r="164" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>166</v>
       </c>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="F164" s="8"/>
     </row>
-    <row r="165" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>160</v>
       </c>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="F165" s="8"/>
     </row>
-    <row r="166" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>154</v>
       </c>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="F166" s="8"/>
     </row>
-    <row r="167" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>156</v>
       </c>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="F167" s="8"/>
     </row>
-    <row r="168" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
         <v>157</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>158</v>
       </c>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="F169" s="8"/>
     </row>
-    <row r="170" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>159</v>
       </c>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F170" s="8"/>
     </row>
-    <row r="171" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>162</v>
       </c>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="F171" s="8"/>
     </row>
-    <row r="172" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>223</v>
       </c>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="F172" s="8"/>
     </row>
-    <row r="173" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>182</v>
       </c>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="F173" s="8"/>
     </row>
-    <row r="174" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>224</v>
       </c>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="F174" s="8"/>
     </row>
-    <row r="175" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>226</v>
       </c>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="F175" s="8"/>
     </row>
-    <row r="176" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>227</v>
       </c>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F176" s="8"/>
     </row>
-    <row r="177" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>229</v>
       </c>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="F177" s="8"/>
     </row>
-    <row r="178" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>172</v>
       </c>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="F178" s="8"/>
     </row>
-    <row r="179" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
         <v>174</v>
       </c>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="F179" s="8"/>
     </row>
-    <row r="180" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
         <v>180</v>
       </c>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="F180" s="8"/>
     </row>
-    <row r="181" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>230</v>
       </c>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="F181" s="8"/>
     </row>
-    <row r="182" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
         <v>186</v>
       </c>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="F182" s="8"/>
     </row>
-    <row r="183" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
         <v>114</v>
       </c>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="F183" s="8"/>
     </row>
-    <row r="184" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
         <v>115</v>
       </c>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="F184" s="8"/>
     </row>
-    <row r="185" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
         <v>116</v>
       </c>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="F185" s="8"/>
     </row>
-    <row r="186" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>232</v>
       </c>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="F186" s="8"/>
     </row>
-    <row r="187" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
         <v>233</v>
       </c>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="F187" s="8"/>
     </row>
-    <row r="188" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
         <v>235</v>
       </c>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F188" s="8"/>
     </row>
-    <row r="189" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
         <v>237</v>
       </c>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="F189" s="8"/>
     </row>
-    <row r="190" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
         <v>235</v>
       </c>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="F190" s="8"/>
     </row>
-    <row r="191" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
         <v>237</v>
       </c>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="F191" s="8"/>
     </row>
-    <row r="192" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>239</v>
       </c>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="F192" s="8"/>
     </row>
-    <row r="193" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>240</v>
       </c>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F193" s="8"/>
     </row>
-    <row r="194" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
         <v>241</v>
       </c>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F194" s="8"/>
     </row>
-    <row r="195" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
         <v>242</v>
       </c>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="F195" s="8"/>
     </row>
-    <row r="196" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
         <v>243</v>
       </c>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="F196" s="8"/>
     </row>
-    <row r="197" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
         <v>244</v>
       </c>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="F197" s="8"/>
     </row>
-    <row r="198" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>245</v>
       </c>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="F198" s="8"/>
     </row>
-    <row r="199" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
         <v>246</v>
       </c>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F199" s="8"/>
     </row>
-    <row r="200" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>247</v>
       </c>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="F200" s="8"/>
     </row>
-    <row r="201" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
         <v>248</v>
       </c>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F201" s="8"/>
     </row>
-    <row r="202" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>249</v>
       </c>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F202" s="8"/>
     </row>
-    <row r="203" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
         <v>250</v>
       </c>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="F203" s="8"/>
     </row>
-    <row r="204" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>251</v>
       </c>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="F204" s="8"/>
     </row>
-    <row r="205" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
         <v>252</v>
       </c>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="F205" s="8"/>
     </row>
-    <row r="206" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>253</v>
       </c>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>254</v>
       </c>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="F207" s="8"/>
     </row>
-    <row r="208" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
         <v>239</v>
       </c>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>256</v>
       </c>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>241</v>
       </c>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F210" s="8"/>
     </row>
-    <row r="211" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
         <v>242</v>
       </c>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="F211" s="8"/>
     </row>
-    <row r="212" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>240</v>
       </c>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="F212" s="8"/>
     </row>
-    <row r="213" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>249</v>
       </c>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F213" s="8"/>
     </row>
-    <row r="214" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
         <v>248</v>
       </c>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="F214" s="8"/>
     </row>
-    <row r="215" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
         <v>257</v>
       </c>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="F215" s="8"/>
     </row>
-    <row r="216" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
         <v>258</v>
       </c>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="F216" s="8"/>
     </row>
-    <row r="217" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
         <v>259</v>
       </c>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="F217" s="8"/>
     </row>
-    <row r="218" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
         <v>246</v>
       </c>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="F218" s="8"/>
     </row>
-    <row r="219" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
         <v>247</v>
       </c>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="F219" s="8"/>
     </row>
-    <row r="220" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
         <v>244</v>
       </c>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="F220" s="8"/>
     </row>
-    <row r="221" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
         <v>245</v>
       </c>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="F221" s="8"/>
     </row>
-    <row r="222" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
         <v>260</v>
       </c>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="F222" s="8"/>
     </row>
-    <row r="223" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
         <v>261</v>
       </c>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="F223" s="8"/>
     </row>
-    <row r="224" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
         <v>263</v>
       </c>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="F224" s="8"/>
     </row>
-    <row r="225" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
         <v>264</v>
       </c>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="F225" s="8"/>
     </row>
-    <row r="226" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>265</v>
       </c>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="F226" s="8"/>
     </row>
-    <row r="227" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
         <v>267</v>
       </c>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="F227" s="8"/>
     </row>
-    <row r="228" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
         <v>268</v>
       </c>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="F228" s="8"/>
     </row>
-    <row r="229" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>269</v>
       </c>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="F229" s="8"/>
     </row>
-    <row r="230" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>270</v>
       </c>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="F230" s="8"/>
     </row>
-    <row r="231" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
         <v>253</v>
       </c>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="F231" s="8"/>
     </row>
-    <row r="232" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>271</v>
       </c>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F232" s="8"/>
     </row>
-    <row r="233" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>273</v>
       </c>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="F233" s="8"/>
     </row>
-    <row r="234" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>274</v>
       </c>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="F234" s="8"/>
     </row>
-    <row r="235" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>275</v>
       </c>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="F235" s="8"/>
     </row>
-    <row r="236" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>276</v>
       </c>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="F236" s="8"/>
     </row>
-    <row r="237" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>277</v>
       </c>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F237" s="8"/>
     </row>
-    <row r="238" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>279</v>
       </c>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F238" s="8"/>
     </row>
-    <row r="239" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
         <v>281</v>
       </c>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="F239" s="8"/>
     </row>
-    <row r="240" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
         <v>282</v>
       </c>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="F240" s="8"/>
     </row>
-    <row r="241" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
         <v>283</v>
       </c>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="F241" s="8"/>
     </row>
-    <row r="242" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>285</v>
       </c>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="F242" s="8"/>
     </row>
-    <row r="243" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
         <v>264</v>
       </c>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="F243" s="8"/>
     </row>
-    <row r="244" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
         <v>263</v>
       </c>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="F244" s="8"/>
     </row>
-    <row r="245" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
         <v>260</v>
       </c>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="F245" s="8"/>
     </row>
-    <row r="246" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
         <v>261</v>
       </c>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="F246" s="8"/>
     </row>
-    <row r="247" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
         <v>287</v>
       </c>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
         <v>289</v>
       </c>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="F248" s="8"/>
     </row>
-    <row r="249" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
         <v>269</v>
       </c>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="F249" s="8"/>
     </row>
-    <row r="250" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
         <v>265</v>
       </c>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="F250" s="8"/>
     </row>
-    <row r="251" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
         <v>290</v>
       </c>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="F251" s="8"/>
     </row>
-    <row r="252" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
         <v>292</v>
       </c>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="F252" s="8"/>
     </row>
-    <row r="253" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
         <v>293</v>
       </c>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="F253" s="8"/>
     </row>
-    <row r="254" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
         <v>294</v>
       </c>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="F254" s="8"/>
     </row>
-    <row r="255" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
         <v>295</v>
       </c>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="F255" s="8"/>
     </row>
-    <row r="256" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
         <v>296</v>
       </c>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F256" s="8"/>
     </row>
-    <row r="257" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
         <v>297</v>
       </c>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="F257" s="8"/>
     </row>
-    <row r="258" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
         <v>298</v>
       </c>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="F258" s="8"/>
     </row>
-    <row r="259" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
         <v>299</v>
       </c>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="F259" s="8"/>
     </row>
-    <row r="260" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
         <v>301</v>
       </c>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="F260" s="8"/>
     </row>
-    <row r="261" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
         <v>302</v>
       </c>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="F261" s="8"/>
     </row>
-    <row r="262" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
         <v>290</v>
       </c>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="F262" s="8"/>
     </row>
-    <row r="263" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
         <v>303</v>
       </c>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F263" s="8"/>
     </row>
-    <row r="264" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
         <v>304</v>
       </c>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="F264" s="8"/>
     </row>
-    <row r="265" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
         <v>306</v>
       </c>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
         <v>308</v>
       </c>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="F266" s="8"/>
     </row>
-    <row r="267" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
         <v>302</v>
       </c>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="F267" s="8"/>
     </row>
-    <row r="268" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
         <v>301</v>
       </c>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="F268" s="8"/>
     </row>
-    <row r="269" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
         <v>309</v>
       </c>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="F269" s="8"/>
     </row>
-    <row r="270" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
         <v>311</v>
       </c>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="F270" s="8"/>
     </row>
-    <row r="271" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
         <v>299</v>
       </c>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="F271" s="8"/>
     </row>
-    <row r="272" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
         <v>312</v>
       </c>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="F272" s="8"/>
     </row>
-    <row r="273" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
         <v>313</v>
       </c>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
         <v>314</v>
       </c>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="F274" s="8"/>
     </row>
-    <row r="275" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
         <v>316</v>
       </c>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F275" s="8"/>
     </row>
-    <row r="276" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
         <v>317</v>
       </c>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="F276" s="8"/>
     </row>
-    <row r="277" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
         <v>319</v>
       </c>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="F277" s="8"/>
     </row>
-    <row r="278" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
         <v>320</v>
       </c>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="F278" s="8"/>
     </row>
-    <row r="279" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
         <v>321</v>
       </c>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="F279" s="8"/>
     </row>
-    <row r="280" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
         <v>322</v>
       </c>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="F280" s="8"/>
     </row>
-    <row r="281" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
         <v>323</v>
       </c>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="F281" s="8"/>
     </row>
-    <row r="282" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
         <v>319</v>
       </c>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="F282" s="8"/>
     </row>
-    <row r="283" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="5" t="s">
         <v>324</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="284" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
         <v>325</v>
       </c>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="F284" s="8"/>
     </row>
-    <row r="285" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
         <v>327</v>
       </c>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="F285" s="8"/>
     </row>
-    <row r="286" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
         <v>328</v>
       </c>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="F286" s="8"/>
     </row>
-    <row r="287" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
         <v>329</v>
       </c>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="F287" s="8"/>
     </row>
-    <row r="288" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
         <v>330</v>
       </c>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="F288" s="8"/>
     </row>
-    <row r="289" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
         <v>331</v>
       </c>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="F289" s="8"/>
     </row>
-    <row r="290" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
         <v>333</v>
       </c>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="F290" s="8"/>
     </row>
-    <row r="291" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
         <v>334</v>
       </c>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="F291" s="8"/>
     </row>
-    <row r="292" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
         <v>335</v>
       </c>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="F292" s="8"/>
     </row>
-    <row r="293" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
         <v>336</v>
       </c>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="F293" s="8"/>
     </row>
-    <row r="294" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
         <v>338</v>
       </c>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F294" s="8"/>
     </row>
-    <row r="295" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
         <v>339</v>
       </c>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F295" s="8"/>
     </row>
-    <row r="296" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
         <v>341</v>
       </c>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="F296" s="8"/>
     </row>
-    <row r="297" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
         <v>342</v>
       </c>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="F297" s="8"/>
     </row>
-    <row r="298" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
         <v>343</v>
       </c>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="F298" s="8"/>
     </row>
-    <row r="299" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
         <v>344</v>
       </c>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="F299" s="8"/>
     </row>
-    <row r="300" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="4" t="s">
         <v>345</v>
       </c>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="F300" s="8"/>
     </row>
-    <row r="301" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
         <v>346</v>
       </c>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="F301" s="8"/>
     </row>
-    <row r="302" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
         <v>347</v>
       </c>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="F302" s="8"/>
     </row>
-    <row r="303" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
         <v>348</v>
       </c>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F303" s="8"/>
     </row>
-    <row r="304" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
         <v>349</v>
       </c>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="F304" s="8"/>
     </row>
-    <row r="305" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
         <v>350</v>
       </c>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="F305" s="8"/>
     </row>
-    <row r="306" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
         <v>351</v>
       </c>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="F306" s="8"/>
     </row>
-    <row r="307" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
         <v>352</v>
       </c>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="F307" s="8"/>
     </row>
-    <row r="308" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
         <v>353</v>
       </c>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="F308" s="8"/>
     </row>
-    <row r="309" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
         <v>354</v>
       </c>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F309" s="8"/>
     </row>
-    <row r="310" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
         <v>355</v>
       </c>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="F310" s="8"/>
     </row>
-    <row r="311" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
         <v>356</v>
       </c>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="F311" s="8"/>
     </row>
-    <row r="312" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
         <v>357</v>
       </c>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="F312" s="8"/>
     </row>
-    <row r="313" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
         <v>358</v>
       </c>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="F313" s="8"/>
     </row>
-    <row r="314" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
         <v>359</v>
       </c>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="F314" s="8"/>
     </row>
-    <row r="315" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
         <v>361</v>
       </c>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="F315" s="8"/>
     </row>
-    <row r="316" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
         <v>362</v>
       </c>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F316" s="8"/>
     </row>
-    <row r="317" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
         <v>363</v>
       </c>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="F317" s="8"/>
     </row>
-    <row r="318" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
         <v>364</v>
       </c>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="F318" s="8"/>
     </row>
-    <row r="319" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
         <v>365</v>
       </c>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="F319" s="8"/>
     </row>
-    <row r="320" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
         <v>366</v>
       </c>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="F320" s="8"/>
     </row>
-    <row r="321" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
         <v>367</v>
       </c>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="F321" s="8"/>
     </row>
-    <row r="322" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
         <v>368</v>
       </c>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="F322" s="8"/>
     </row>
-    <row r="323" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
         <v>369</v>
       </c>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="F323" s="8"/>
     </row>
-    <row r="324" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="4" t="s">
         <v>370</v>
       </c>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="F324" s="8"/>
     </row>
-    <row r="325" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
         <v>371</v>
       </c>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F325" s="8"/>
     </row>
-    <row r="326" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
         <v>373</v>
       </c>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F326" s="8"/>
     </row>
-    <row r="327" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
         <v>374</v>
       </c>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="F327" s="8"/>
     </row>
-    <row r="328" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
         <v>375</v>
       </c>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="F328" s="8"/>
     </row>
-    <row r="329" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
         <v>376</v>
       </c>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="F329" s="8"/>
     </row>
-    <row r="330" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
         <v>377</v>
       </c>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="F330" s="8"/>
     </row>
-    <row r="331" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
         <v>378</v>
       </c>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="F331" s="8"/>
     </row>
-    <row r="332" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
         <v>379</v>
       </c>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="F332" s="8"/>
     </row>
-    <row r="333" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
         <v>380</v>
       </c>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="F333" s="8"/>
     </row>
-    <row r="334" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="4" t="s">
         <v>381</v>
       </c>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="F334" s="8"/>
     </row>
-    <row r="335" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
         <v>382</v>
       </c>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="F335" s="8"/>
     </row>
-    <row r="336" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
         <v>384</v>
       </c>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="F336" s="8"/>
     </row>
-    <row r="337" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
         <v>385</v>
       </c>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="F337" s="8"/>
     </row>
-    <row r="338" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
         <v>386</v>
       </c>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="F338" s="8"/>
     </row>
-    <row r="339" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="4" t="s">
         <v>387</v>
       </c>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="F339" s="8"/>
     </row>
-    <row r="340" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="4" t="s">
         <v>389</v>
       </c>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="F340" s="8"/>
     </row>
-    <row r="341" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
         <v>390</v>
       </c>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="F341" s="8"/>
     </row>
-    <row r="342" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
         <v>391</v>
       </c>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="F342" s="8"/>
     </row>
-    <row r="343" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
         <v>392</v>
       </c>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="F343" s="8"/>
     </row>
-    <row r="344" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="4" t="s">
         <v>393</v>
       </c>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="F344" s="8"/>
     </row>
-    <row r="345" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
         <v>394</v>
       </c>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="F345" s="8"/>
     </row>
-    <row r="346" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
         <v>395</v>
       </c>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="F346" s="8"/>
     </row>
-    <row r="347" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
         <v>397</v>
       </c>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="F347" s="8"/>
     </row>
-    <row r="348" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
         <v>398</v>
       </c>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="F348" s="8"/>
     </row>
-    <row r="349" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="4" t="s">
         <v>400</v>
       </c>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="F349" s="8"/>
     </row>
-    <row r="350" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
         <v>335</v>
       </c>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="F350" s="8"/>
     </row>
-    <row r="351" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="4" t="s">
         <v>401</v>
       </c>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="F351" s="8"/>
     </row>
-    <row r="352" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
         <v>402</v>
       </c>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="F352" s="8"/>
     </row>
-    <row r="353" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
         <v>403</v>
       </c>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="F353" s="8"/>
     </row>
-    <row r="354" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="4" t="s">
         <v>405</v>
       </c>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="F354" s="8"/>
     </row>
-    <row r="355" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="4" t="s">
         <v>406</v>
       </c>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="F355" s="8"/>
     </row>
-    <row r="356" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
         <v>408</v>
       </c>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F356" s="8"/>
     </row>
-    <row r="357" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
         <v>342</v>
       </c>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F357" s="8"/>
     </row>
-    <row r="358" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
         <v>350</v>
       </c>
@@ -9628,7 +9628,7 @@
       </c>
       <c r="F358" s="8"/>
     </row>
-    <row r="359" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
         <v>361</v>
       </c>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="F359" s="8"/>
     </row>
-    <row r="360" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
         <v>349</v>
       </c>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="F360" s="8"/>
     </row>
-    <row r="361" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
         <v>348</v>
       </c>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="F361" s="8"/>
     </row>
-    <row r="362" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="4" t="s">
         <v>355</v>
       </c>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="F362" s="8"/>
     </row>
-    <row r="363" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="4" t="s">
         <v>353</v>
       </c>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="F363" s="8"/>
     </row>
-    <row r="364" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
         <v>347</v>
       </c>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="F364" s="8"/>
     </row>
-    <row r="365" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="4" t="s">
         <v>341</v>
       </c>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="F365" s="8"/>
     </row>
-    <row r="366" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="4" t="s">
         <v>346</v>
       </c>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="F366" s="8"/>
     </row>
-    <row r="367" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="4" t="s">
         <v>352</v>
       </c>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="F367" s="8"/>
     </row>
-    <row r="368" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
         <v>345</v>
       </c>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="F368" s="8"/>
     </row>
-    <row r="369" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="4" t="s">
         <v>356</v>
       </c>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="F369" s="8"/>
     </row>
-    <row r="370" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="4" t="s">
         <v>343</v>
       </c>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="F370" s="8"/>
     </row>
-    <row r="371" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
         <v>354</v>
       </c>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="F371" s="8"/>
     </row>
-    <row r="372" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="4" t="s">
         <v>344</v>
       </c>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="F372" s="8"/>
     </row>
-    <row r="373" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
         <v>351</v>
       </c>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="F373" s="8"/>
     </row>
-    <row r="374" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="4" t="s">
         <v>409</v>
       </c>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="F374" s="8"/>
     </row>
-    <row r="375" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="4" t="s">
         <v>338</v>
       </c>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="F375" s="8"/>
     </row>
-    <row r="376" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
         <v>336</v>
       </c>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="F376" s="8"/>
     </row>
-    <row r="377" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
         <v>339</v>
       </c>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="F377" s="8"/>
     </row>
-    <row r="378" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
         <v>410</v>
       </c>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="F378" s="8"/>
     </row>
-    <row r="379" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="4" t="s">
         <v>411</v>
       </c>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="F379" s="8"/>
     </row>
-    <row r="380" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="4" t="s">
         <v>412</v>
       </c>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="F380" s="8"/>
     </row>
-    <row r="381" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="4" t="s">
         <v>413</v>
       </c>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="F381" s="8"/>
     </row>
-    <row r="382" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
         <v>367</v>
       </c>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="F382" s="8"/>
     </row>
-    <row r="383" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="4" t="s">
         <v>369</v>
       </c>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="F383" s="8"/>
     </row>
-    <row r="384" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="4" t="s">
         <v>373</v>
       </c>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="F384" s="8"/>
     </row>
-    <row r="385" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="4" t="s">
         <v>370</v>
       </c>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="F385" s="8"/>
     </row>
-    <row r="386" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="4" t="s">
         <v>371</v>
       </c>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="F386" s="8"/>
     </row>
-    <row r="387" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
         <v>366</v>
       </c>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F387" s="8"/>
     </row>
-    <row r="388" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
         <v>365</v>
       </c>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="F388" s="8"/>
     </row>
-    <row r="389" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
         <v>415</v>
       </c>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="F389" s="8"/>
     </row>
-    <row r="390" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="4" t="s">
         <v>416</v>
       </c>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="F390" s="8"/>
     </row>
-    <row r="391" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="4" t="s">
         <v>368</v>
       </c>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="F391" s="8"/>
     </row>
-    <row r="392" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="4" t="s">
         <v>364</v>
       </c>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="F392" s="8"/>
     </row>
-    <row r="393" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
         <v>362</v>
       </c>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="F393" s="8"/>
     </row>
-    <row r="394" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="4" t="s">
         <v>363</v>
       </c>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="4" t="s">
         <v>417</v>
       </c>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="4" t="s">
         <v>418</v>
       </c>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="4" t="s">
         <v>419</v>
       </c>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="F397" s="8"/>
     </row>
-    <row r="398" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="4" t="s">
         <v>420</v>
       </c>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="F398" s="8"/>
     </row>
-    <row r="399" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
         <v>421</v>
       </c>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="F399" s="8"/>
     </row>
-    <row r="400" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
         <v>422</v>
       </c>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="F400" s="8"/>
     </row>
-    <row r="401" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="4" t="s">
         <v>423</v>
       </c>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="F401" s="8"/>
     </row>
-    <row r="402" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
         <v>424</v>
       </c>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="F402" s="8"/>
     </row>
-    <row r="403" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="4" t="s">
         <v>425</v>
       </c>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="F403" s="8"/>
     </row>
-    <row r="404" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
         <v>426</v>
       </c>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="F404" s="8"/>
     </row>
-    <row r="405" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="4" t="s">
         <v>427</v>
       </c>
@@ -10474,7 +10474,7 @@
       </c>
       <c r="F405" s="8"/>
     </row>
-    <row r="406" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="4" t="s">
         <v>428</v>
       </c>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
         <v>429</v>
       </c>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="F407" s="8"/>
     </row>
-    <row r="408" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
         <v>431</v>
       </c>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="F408" s="8"/>
     </row>
-    <row r="409" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="4" t="s">
         <v>433</v>
       </c>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="F409" s="8"/>
     </row>
-    <row r="410" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="4" t="s">
         <v>435</v>
       </c>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="F410" s="8"/>
     </row>
-    <row r="411" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="4" t="s">
         <v>436</v>
       </c>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="F411" s="8"/>
     </row>
-    <row r="412" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="4" t="s">
         <v>438</v>
       </c>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="F412" s="8"/>
     </row>
-    <row r="413" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:6" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="5" t="s">
         <v>439</v>
       </c>
@@ -10620,7 +10620,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="414" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="4" t="s">
         <v>440</v>
       </c>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="F414" s="8"/>
     </row>
-    <row r="415" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="4" t="s">
         <v>441</v>
       </c>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="F415" s="8"/>
     </row>
-    <row r="416" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="4" t="s">
         <v>442</v>
       </c>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="F416" s="8"/>
     </row>
-    <row r="417" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
         <v>443</v>
       </c>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="F417" s="8"/>
     </row>
-    <row r="418" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="4" t="s">
         <v>444</v>
       </c>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="F418" s="8"/>
     </row>
-    <row r="419" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="4" t="s">
         <v>446</v>
       </c>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="F419" s="8"/>
     </row>
-    <row r="420" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="4" t="s">
         <v>447</v>
       </c>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="F420" s="8"/>
     </row>
-    <row r="421" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="4" t="s">
         <v>448</v>
       </c>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="F421" s="8"/>
     </row>
-    <row r="422" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="4" t="s">
         <v>391</v>
       </c>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="F422" s="8"/>
     </row>
-    <row r="423" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="4" t="s">
         <v>392</v>
       </c>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="F423" s="8"/>
     </row>
-    <row r="424" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="4" t="s">
         <v>393</v>
       </c>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="F424" s="8"/>
     </row>
-    <row r="425" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
         <v>394</v>
       </c>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="F425" s="8"/>
     </row>
-    <row r="426" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="4" t="s">
         <v>401</v>
       </c>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="F426" s="8"/>
     </row>
-    <row r="427" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="4" t="s">
         <v>335</v>
       </c>
@@ -10872,7 +10872,7 @@
       </c>
       <c r="F427" s="8"/>
     </row>
-    <row r="428" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="4" t="s">
         <v>403</v>
       </c>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="F428" s="8"/>
     </row>
-    <row r="429" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="4" t="s">
         <v>402</v>
       </c>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="F429" s="8"/>
     </row>
-    <row r="430" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="4" t="s">
         <v>406</v>
       </c>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="F430" s="8"/>
     </row>
-    <row r="431" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="4" t="s">
         <v>405</v>
       </c>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
         <v>389</v>
       </c>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="F432" s="8"/>
     </row>
-    <row r="433" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
         <v>390</v>
       </c>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="F433" s="8"/>
     </row>
-    <row r="434" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="4" t="s">
         <v>450</v>
       </c>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="F434" s="8"/>
     </row>
-    <row r="435" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="4" t="s">
         <v>387</v>
       </c>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F435" s="8"/>
     </row>
-    <row r="436" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="4" t="s">
         <v>451</v>
       </c>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="F436" s="8"/>
     </row>
-    <row r="437" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="4" t="s">
         <v>452</v>
       </c>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="F437" s="8"/>
     </row>
-    <row r="438" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="4" t="s">
         <v>453</v>
       </c>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="F438" s="8"/>
     </row>
-    <row r="439" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="4" t="s">
         <v>454</v>
       </c>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F439" s="8"/>
     </row>
-    <row r="440" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="4" t="s">
         <v>456</v>
       </c>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="F440" s="8"/>
     </row>
-    <row r="441" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="4" t="s">
         <v>457</v>
       </c>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="F441" s="8"/>
     </row>
-    <row r="442" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="4" t="s">
         <v>459</v>
       </c>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="4" t="s">
         <v>461</v>
       </c>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="F443" s="8"/>
     </row>
-    <row r="444" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
         <v>463</v>
       </c>
@@ -11178,7 +11178,7 @@
       </c>
       <c r="F444" s="8"/>
     </row>
-    <row r="445" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
         <v>465</v>
       </c>
@@ -11196,7 +11196,7 @@
       </c>
       <c r="F445" s="8"/>
     </row>
-    <row r="446" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="4" t="s">
         <v>466</v>
       </c>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="F446" s="8"/>
     </row>
-    <row r="447" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="4" t="s">
         <v>468</v>
       </c>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="F447" s="8"/>
     </row>
-    <row r="448" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="4" t="s">
         <v>470</v>
       </c>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="F448" s="8"/>
     </row>
-    <row r="449" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="4" t="s">
         <v>471</v>
       </c>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="F449" s="8"/>
     </row>
-    <row r="450" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
         <v>472</v>
       </c>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="F450" s="8"/>
     </row>
-    <row r="451" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="4" t="s">
         <v>473</v>
       </c>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
         <v>474</v>
       </c>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="F452" s="8"/>
     </row>
-    <row r="453" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="4" t="s">
         <v>475</v>
       </c>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="F453" s="8"/>
     </row>
-    <row r="454" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="4" t="s">
         <v>477</v>
       </c>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="F454" s="8"/>
     </row>
-    <row r="455" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="4" t="s">
         <v>478</v>
       </c>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="F455" s="8"/>
     </row>
-    <row r="456" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="4" t="s">
         <v>479</v>
       </c>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="F456" s="8"/>
     </row>
-    <row r="457" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="4" t="s">
         <v>480</v>
       </c>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="F457" s="8"/>
     </row>
-    <row r="458" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="4" t="s">
         <v>481</v>
       </c>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="F458" s="8"/>
     </row>
-    <row r="459" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="4" t="s">
         <v>482</v>
       </c>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F459" s="8"/>
     </row>
-    <row r="460" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="4" t="s">
         <v>483</v>
       </c>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="F460" s="8"/>
     </row>
-    <row r="461" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="4" t="s">
         <v>484</v>
       </c>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="F461" s="8"/>
     </row>
-    <row r="462" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="4" t="s">
         <v>485</v>
       </c>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="F462" s="8"/>
     </row>
-    <row r="463" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="4" t="s">
         <v>486</v>
       </c>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="F463" s="8"/>
     </row>
-    <row r="464" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="4" t="s">
         <v>425</v>
       </c>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="F464" s="8"/>
     </row>
-    <row r="465" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
         <v>426</v>
       </c>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="F465" s="8"/>
     </row>
-    <row r="466" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="4" t="s">
         <v>427</v>
       </c>
@@ -11574,7 +11574,7 @@
       </c>
       <c r="F466" s="8"/>
     </row>
-    <row r="467" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="4" t="s">
         <v>424</v>
       </c>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="F467" s="8"/>
     </row>
-    <row r="468" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="4" t="s">
         <v>428</v>
       </c>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="F468" s="8"/>
     </row>
-    <row r="469" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="4" t="s">
         <v>417</v>
       </c>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="F469" s="8"/>
     </row>
-    <row r="470" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="4" t="s">
         <v>418</v>
       </c>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="F470" s="8"/>
     </row>
-    <row r="471" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="4" t="s">
         <v>419</v>
       </c>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="F471" s="8"/>
     </row>
-    <row r="472" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="4" t="s">
         <v>420</v>
       </c>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="F472" s="8"/>
     </row>
-    <row r="473" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="4" t="s">
         <v>421</v>
       </c>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="F473" s="8"/>
     </row>
-    <row r="474" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="4" t="s">
         <v>422</v>
       </c>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="F474" s="8"/>
     </row>
-    <row r="475" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="4" t="s">
         <v>423</v>
       </c>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F475" s="8"/>
     </row>
-    <row r="476" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="4" t="s">
         <v>438</v>
       </c>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="F476" s="8"/>
     </row>
-    <row r="477" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="4" t="s">
         <v>446</v>
       </c>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="F477" s="8"/>
     </row>
-    <row r="478" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="4" t="s">
         <v>443</v>
       </c>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="F478" s="8"/>
     </row>
-    <row r="479" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="4" t="s">
         <v>442</v>
       </c>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="F479" s="8"/>
     </row>
-    <row r="480" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="4" t="s">
         <v>444</v>
       </c>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="F480" s="8"/>
     </row>
-    <row r="481" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
         <v>447</v>
       </c>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="F481" s="8"/>
     </row>
-    <row r="482" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="4" t="s">
         <v>440</v>
       </c>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="F482" s="8"/>
     </row>
-    <row r="483" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="4" t="s">
         <v>441</v>
       </c>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="F483" s="8"/>
     </row>
-    <row r="484" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="4" t="s">
         <v>488</v>
       </c>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="F484" s="8"/>
     </row>
-    <row r="485" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="4" t="s">
         <v>489</v>
       </c>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="F485" s="8"/>
     </row>
-    <row r="486" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="4" t="s">
         <v>490</v>
       </c>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="F486" s="8"/>
     </row>
-    <row r="487" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="4" t="s">
         <v>491</v>
       </c>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F487" s="8"/>
     </row>
-    <row r="488" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="4" t="s">
         <v>492</v>
       </c>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="F488" s="8"/>
     </row>
-    <row r="489" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="4" t="s">
         <v>493</v>
       </c>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="F489" s="8"/>
     </row>
-    <row r="490" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="4" t="s">
         <v>431</v>
       </c>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="F490" s="8"/>
     </row>
-    <row r="491" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="4" t="s">
         <v>433</v>
       </c>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="F491" s="8"/>
     </row>
-    <row r="492" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="4" t="s">
         <v>429</v>
       </c>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="F492" s="8"/>
     </row>
-    <row r="493" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
         <v>435</v>
       </c>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="F493" s="8"/>
     </row>
-    <row r="494" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="4" t="s">
         <v>439</v>
       </c>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F494" s="8"/>
     </row>
-    <row r="495" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="4" t="s">
         <v>448</v>
       </c>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="F495" s="8"/>
     </row>
-    <row r="496" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="4" t="s">
         <v>391</v>
       </c>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="F496" s="8"/>
     </row>
-    <row r="497" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="4" t="s">
         <v>392</v>
       </c>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="F497" s="8"/>
     </row>
-    <row r="498" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="4" t="s">
         <v>394</v>
       </c>
@@ -12150,7 +12150,7 @@
       </c>
       <c r="F498" s="8"/>
     </row>
-    <row r="499" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="4" t="s">
         <v>393</v>
       </c>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="F499" s="8"/>
     </row>
-    <row r="500" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="4" t="s">
         <v>495</v>
       </c>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="F500" s="8"/>
     </row>
-    <row r="501" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="4" t="s">
         <v>497</v>
       </c>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="F501" s="8"/>
     </row>
-    <row r="502" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="4" t="s">
         <v>498</v>
       </c>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="F502" s="8"/>
     </row>
-    <row r="503" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="4" t="s">
         <v>499</v>
       </c>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="F503" s="8"/>
     </row>
-    <row r="504" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="4" t="s">
         <v>500</v>
       </c>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="F504" s="8"/>
     </row>
-    <row r="505" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="4" t="s">
         <v>501</v>
       </c>
@@ -12276,7 +12276,7 @@
       </c>
       <c r="F505" s="8"/>
     </row>
-    <row r="506" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="4" t="s">
         <v>502</v>
       </c>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="F506" s="8"/>
     </row>
-    <row r="507" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="4" t="s">
         <v>503</v>
       </c>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="F507" s="8"/>
     </row>
-    <row r="508" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="4" t="s">
         <v>504</v>
       </c>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="F508" s="8"/>
     </row>
-    <row r="509" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="4" t="s">
         <v>505</v>
       </c>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="F509" s="8"/>
     </row>
-    <row r="510" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="4" t="s">
         <v>506</v>
       </c>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="F510" s="8"/>
     </row>
-    <row r="511" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="4" t="s">
         <v>507</v>
       </c>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="F511" s="8"/>
     </row>
-    <row r="512" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="4" t="s">
         <v>508</v>
       </c>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="F512" s="8"/>
     </row>
-    <row r="513" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="4" t="s">
         <v>509</v>
       </c>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="F513" s="8"/>
     </row>
-    <row r="514" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="4" t="s">
         <v>510</v>
       </c>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="F514" s="8"/>
     </row>
-    <row r="515" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="4" t="s">
         <v>511</v>
       </c>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F515" s="8"/>
     </row>
-    <row r="516" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="4" t="s">
         <v>512</v>
       </c>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="F516" s="8"/>
     </row>
-    <row r="517" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="4" t="s">
         <v>513</v>
       </c>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="F517" s="8"/>
     </row>
-    <row r="518" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="4" t="s">
         <v>514</v>
       </c>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F518" s="8"/>
     </row>
-    <row r="519" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="4" t="s">
         <v>515</v>
       </c>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="F519" s="8"/>
     </row>
-    <row r="520" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="4" t="s">
         <v>516</v>
       </c>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="F520" s="8"/>
     </row>
-    <row r="521" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="4" t="s">
         <v>517</v>
       </c>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="F521" s="8"/>
     </row>
-    <row r="522" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="4" t="s">
         <v>518</v>
       </c>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="F522" s="8"/>
     </row>
-    <row r="523" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="4" t="s">
         <v>519</v>
       </c>
@@ -12600,7 +12600,7 @@
       </c>
       <c r="F523" s="8"/>
     </row>
-    <row r="524" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="4" t="s">
         <v>520</v>
       </c>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="F524" s="8"/>
     </row>
-    <row r="525" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="4" t="s">
         <v>521</v>
       </c>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="F525" s="8"/>
     </row>
-    <row r="526" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="4" t="s">
         <v>522</v>
       </c>
@@ -12654,7 +12654,7 @@
       </c>
       <c r="F526" s="8"/>
     </row>
-    <row r="527" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="4" t="s">
         <v>523</v>
       </c>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="F527" s="8"/>
     </row>
-    <row r="528" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="4" t="s">
         <v>524</v>
       </c>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="F528" s="8"/>
     </row>
-    <row r="529" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="4" t="s">
         <v>525</v>
       </c>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="F529" s="8"/>
     </row>
-    <row r="530" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="4" t="s">
         <v>526</v>
       </c>
@@ -12726,7 +12726,7 @@
       </c>
       <c r="F530" s="8"/>
     </row>
-    <row r="531" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="4" t="s">
         <v>527</v>
       </c>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F531" s="8"/>
     </row>
-    <row r="532" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="4" t="s">
         <v>529</v>
       </c>
@@ -12762,7 +12762,7 @@
       </c>
       <c r="F532" s="8"/>
     </row>
-    <row r="533" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="4" t="s">
         <v>530</v>
       </c>
@@ -12780,7 +12780,7 @@
       </c>
       <c r="F533" s="8"/>
     </row>
-    <row r="534" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="4" t="s">
         <v>531</v>
       </c>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="F534" s="8"/>
     </row>
-    <row r="535" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="4" t="s">
         <v>532</v>
       </c>
@@ -12816,7 +12816,7 @@
       </c>
       <c r="F535" s="8"/>
     </row>
-    <row r="536" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="4" t="s">
         <v>533</v>
       </c>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="F536" s="8"/>
     </row>
-    <row r="537" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="4" t="s">
         <v>534</v>
       </c>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="F537" s="8"/>
     </row>
-    <row r="538" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="4" t="s">
         <v>535</v>
       </c>
@@ -12870,7 +12870,7 @@
       </c>
       <c r="F538" s="8"/>
     </row>
-    <row r="539" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="4" t="s">
         <v>536</v>
       </c>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="F539" s="8"/>
     </row>
-    <row r="540" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="4" t="s">
         <v>537</v>
       </c>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="F540" s="8"/>
     </row>
-    <row r="541" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="4" t="s">
         <v>538</v>
       </c>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="F541" s="8"/>
     </row>
-    <row r="542" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="4" t="s">
         <v>539</v>
       </c>
@@ -12942,7 +12942,7 @@
       </c>
       <c r="F542" s="8"/>
     </row>
-    <row r="543" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="4" t="s">
         <v>540</v>
       </c>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="F543" s="8"/>
     </row>
-    <row r="544" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="4" t="s">
         <v>542</v>
       </c>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="F544" s="8"/>
     </row>
-    <row r="545" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="4" t="s">
         <v>543</v>
       </c>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F545" s="8"/>
     </row>
-    <row r="546" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="4" t="s">
         <v>544</v>
       </c>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="F546" s="8"/>
     </row>
-    <row r="547" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="4" t="s">
         <v>545</v>
       </c>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F547" s="8"/>
     </row>
-    <row r="548" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="4" t="s">
         <v>499</v>
       </c>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="F548" s="8"/>
     </row>
-    <row r="549" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="4" t="s">
         <v>501</v>
       </c>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="F549" s="8"/>
     </row>
-    <row r="550" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="4" t="s">
         <v>502</v>
       </c>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="F550" s="8"/>
     </row>
-    <row r="551" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="4" t="s">
         <v>503</v>
       </c>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="F551" s="8"/>
     </row>
-    <row r="552" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="4" t="s">
         <v>546</v>
       </c>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="F552" s="8"/>
     </row>
-    <row r="553" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="4" t="s">
         <v>547</v>
       </c>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="F553" s="8"/>
     </row>
-    <row r="554" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="4" t="s">
         <v>548</v>
       </c>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="F554" s="8"/>
     </row>
-    <row r="555" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="4" t="s">
         <v>549</v>
       </c>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="F555" s="8"/>
     </row>
-    <row r="556" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="4" t="s">
         <v>498</v>
       </c>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="F556" s="8"/>
     </row>
-    <row r="557" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="4" t="s">
         <v>513</v>
       </c>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="F557" s="8"/>
     </row>
-    <row r="558" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="4" t="s">
         <v>550</v>
       </c>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="F558" s="8"/>
     </row>
-    <row r="559" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="4" t="s">
         <v>511</v>
       </c>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="F559" s="8"/>
     </row>
-    <row r="560" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="4" t="s">
         <v>512</v>
       </c>
@@ -13266,7 +13266,7 @@
       </c>
       <c r="F560" s="8"/>
     </row>
-    <row r="561" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="4" t="s">
         <v>551</v>
       </c>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="F561" s="8"/>
     </row>
-    <row r="562" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="4" t="s">
         <v>552</v>
       </c>
@@ -13302,7 +13302,7 @@
       </c>
       <c r="F562" s="8"/>
     </row>
-    <row r="563" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="4" t="s">
         <v>553</v>
       </c>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F563" s="8"/>
     </row>
-    <row r="564" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="4" t="s">
         <v>510</v>
       </c>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="F564" s="8"/>
     </row>
-    <row r="565" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="4" t="s">
         <v>554</v>
       </c>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="F565" s="8"/>
     </row>
-    <row r="566" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="4" t="s">
         <v>555</v>
       </c>
@@ -13374,7 +13374,7 @@
       </c>
       <c r="F566" s="8"/>
     </row>
-    <row r="567" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="4" t="s">
         <v>556</v>
       </c>
@@ -13392,7 +13392,7 @@
       </c>
       <c r="F567" s="8"/>
     </row>
-    <row r="568" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="4" t="s">
         <v>557</v>
       </c>
@@ -13410,7 +13410,7 @@
       </c>
       <c r="F568" s="8"/>
     </row>
-    <row r="569" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="4" t="s">
         <v>558</v>
       </c>
@@ -13428,7 +13428,7 @@
       </c>
       <c r="F569" s="8"/>
     </row>
-    <row r="570" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="4" t="s">
         <v>559</v>
       </c>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="F570" s="8"/>
     </row>
-    <row r="571" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="4" t="s">
         <v>561</v>
       </c>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="F571" s="8"/>
     </row>
-    <row r="572" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="4" t="s">
         <v>562</v>
       </c>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="F572" s="8"/>
     </row>
-    <row r="573" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="4" t="s">
         <v>563</v>
       </c>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="F573" s="8"/>
     </row>
-    <row r="574" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="4" t="s">
         <v>564</v>
       </c>
@@ -13518,7 +13518,7 @@
       </c>
       <c r="F574" s="8"/>
     </row>
-    <row r="575" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:6" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="5" t="s">
         <v>565</v>
       </c>
@@ -13538,7 +13538,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="576" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="4" t="s">
         <v>566</v>
       </c>
@@ -13556,7 +13556,7 @@
       </c>
       <c r="F576" s="8"/>
     </row>
-    <row r="577" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="4" t="s">
         <v>567</v>
       </c>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="F577" s="8"/>
     </row>
-    <row r="578" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="4" t="s">
         <v>568</v>
       </c>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="F578" s="8"/>
     </row>
-    <row r="579" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="4" t="s">
         <v>570</v>
       </c>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="F579" s="8"/>
     </row>
-    <row r="580" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="4" t="s">
         <v>571</v>
       </c>
@@ -13628,7 +13628,7 @@
       </c>
       <c r="F580" s="8"/>
     </row>
-    <row r="581" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="4" t="s">
         <v>572</v>
       </c>
@@ -13646,7 +13646,7 @@
       </c>
       <c r="F581" s="8"/>
     </row>
-    <row r="582" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="4" t="s">
         <v>573</v>
       </c>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="F582" s="8"/>
     </row>
-    <row r="583" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="4" t="s">
         <v>574</v>
       </c>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="F583" s="8"/>
     </row>
-    <row r="584" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="4" t="s">
         <v>575</v>
       </c>
@@ -13700,7 +13700,7 @@
       </c>
       <c r="F584" s="8"/>
     </row>
-    <row r="585" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="4" t="s">
         <v>577</v>
       </c>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="F585" s="8"/>
     </row>
-    <row r="586" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="4" t="s">
         <v>538</v>
       </c>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="F586" s="8"/>
     </row>
-    <row r="587" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="4" t="s">
         <v>579</v>
       </c>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="F587" s="8"/>
     </row>
-    <row r="588" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="4" t="s">
         <v>580</v>
       </c>
@@ -13772,7 +13772,7 @@
       </c>
       <c r="F588" s="8"/>
     </row>
-    <row r="589" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="4" t="s">
         <v>545</v>
       </c>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="F589" s="8"/>
     </row>
-    <row r="590" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="4" t="s">
         <v>581</v>
       </c>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="F590" s="8"/>
     </row>
-    <row r="591" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="4" t="s">
         <v>582</v>
       </c>
@@ -13826,7 +13826,7 @@
       </c>
       <c r="F591" s="8"/>
     </row>
-    <row r="592" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="4" t="s">
         <v>583</v>
       </c>
@@ -13844,7 +13844,7 @@
       </c>
       <c r="F592" s="8"/>
     </row>
-    <row r="593" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="4" t="s">
         <v>584</v>
       </c>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="F593" s="8"/>
     </row>
-    <row r="594" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="4" t="s">
         <v>585</v>
       </c>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="F594" s="8"/>
     </row>
-    <row r="595" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="4" t="s">
         <v>587</v>
       </c>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="F595" s="8"/>
     </row>
-    <row r="596" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="4" t="s">
         <v>589</v>
       </c>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F596" s="8"/>
     </row>
-    <row r="597" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="4" t="s">
         <v>590</v>
       </c>
@@ -13934,7 +13934,7 @@
       </c>
       <c r="F597" s="8"/>
     </row>
-    <row r="598" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="4" t="s">
         <v>591</v>
       </c>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="F598" s="8"/>
     </row>
-    <row r="599" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="4" t="s">
         <v>592</v>
       </c>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="F599" s="8"/>
     </row>
-    <row r="600" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="4" t="s">
         <v>594</v>
       </c>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="F600" s="8"/>
     </row>
-    <row r="601" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="4" t="s">
         <v>595</v>
       </c>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="F601" s="8"/>
     </row>
-    <row r="602" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="4" t="s">
         <v>596</v>
       </c>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="F602" s="8"/>
     </row>
-    <row r="603" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="4" t="s">
         <v>598</v>
       </c>
@@ -14042,7 +14042,7 @@
       </c>
       <c r="F603" s="8"/>
     </row>
-    <row r="604" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="4" t="s">
         <v>599</v>
       </c>
@@ -14060,7 +14060,7 @@
       </c>
       <c r="F604" s="8"/>
     </row>
-    <row r="605" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="4" t="s">
         <v>600</v>
       </c>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="F605" s="8"/>
     </row>
-    <row r="606" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="4" t="s">
         <v>602</v>
       </c>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="F606" s="8"/>
     </row>
-    <row r="607" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="4" t="s">
         <v>603</v>
       </c>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="F607" s="8"/>
     </row>
-    <row r="608" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="4" t="s">
         <v>562</v>
       </c>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="F608" s="8"/>
     </row>
-    <row r="609" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="4" t="s">
         <v>563</v>
       </c>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="F609" s="8"/>
     </row>
-    <row r="610" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="4" t="s">
         <v>565</v>
       </c>
@@ -14168,7 +14168,7 @@
       </c>
       <c r="F610" s="8"/>
     </row>
-    <row r="611" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="4" t="s">
         <v>564</v>
       </c>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="F611" s="8"/>
     </row>
-    <row r="612" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="4" t="s">
         <v>555</v>
       </c>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="F612" s="8"/>
     </row>
-    <row r="613" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="4" t="s">
         <v>557</v>
       </c>
@@ -14222,7 +14222,7 @@
       </c>
       <c r="F613" s="8"/>
     </row>
-    <row r="614" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="4" t="s">
         <v>558</v>
       </c>
@@ -14240,7 +14240,7 @@
       </c>
       <c r="F614" s="8"/>
     </row>
-    <row r="615" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="4" t="s">
         <v>554</v>
       </c>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="F615" s="8"/>
     </row>
-    <row r="616" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="4" t="s">
         <v>556</v>
       </c>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="F616" s="8"/>
     </row>
-    <row r="617" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="4" t="s">
         <v>559</v>
       </c>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="F617" s="8"/>
     </row>
-    <row r="618" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="4" t="s">
         <v>561</v>
       </c>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="F618" s="8"/>
     </row>
-    <row r="619" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="4" t="s">
         <v>566</v>
       </c>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="F619" s="8"/>
     </row>
-    <row r="620" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="4" t="s">
         <v>567</v>
       </c>
@@ -14348,7 +14348,7 @@
       </c>
       <c r="F620" s="8"/>
     </row>
-    <row r="621" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="4" t="s">
         <v>605</v>
       </c>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F621" s="8"/>
     </row>
-    <row r="622" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="4" t="s">
         <v>606</v>
       </c>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="F622" s="8"/>
     </row>
-    <row r="623" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="4" t="s">
         <v>608</v>
       </c>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F623" s="8"/>
     </row>
-    <row r="624" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="4" t="s">
         <v>609</v>
       </c>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F624" s="8"/>
     </row>
-    <row r="625" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="4" t="s">
         <v>573</v>
       </c>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="F625" s="8"/>
     </row>
-    <row r="626" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="4" t="s">
         <v>572</v>
       </c>
@@ -14456,7 +14456,7 @@
       </c>
       <c r="F626" s="8"/>
     </row>
-    <row r="627" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="4" t="s">
         <v>538</v>
       </c>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="F627" s="8"/>
     </row>
-    <row r="628" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="4" t="s">
         <v>610</v>
       </c>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="F628" s="8"/>
     </row>
-    <row r="629" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="4" t="s">
         <v>611</v>
       </c>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="F629" s="8"/>
     </row>
-    <row r="630" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="4" t="s">
         <v>613</v>
       </c>
@@ -14528,7 +14528,7 @@
       </c>
       <c r="F630" s="8"/>
     </row>
-    <row r="631" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="4" t="s">
         <v>614</v>
       </c>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="F631" s="8"/>
     </row>
-    <row r="632" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="4" t="s">
         <v>616</v>
       </c>
@@ -14564,7 +14564,7 @@
       </c>
       <c r="F632" s="8"/>
     </row>
-    <row r="633" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="4" t="s">
         <v>577</v>
       </c>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="F633" s="8"/>
     </row>
-    <row r="634" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="4" t="s">
         <v>618</v>
       </c>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="F634" s="8"/>
     </row>
-    <row r="635" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="4" t="s">
         <v>620</v>
       </c>
@@ -14618,7 +14618,7 @@
       </c>
       <c r="F635" s="8"/>
     </row>
-    <row r="636" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="4" t="s">
         <v>621</v>
       </c>
@@ -14636,7 +14636,7 @@
       </c>
       <c r="F636" s="8"/>
     </row>
-    <row r="637" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="4" t="s">
         <v>622</v>
       </c>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="F637" s="8"/>
     </row>
-    <row r="638" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="4" t="s">
         <v>623</v>
       </c>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="F638" s="8"/>
     </row>
-    <row r="639" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="4" t="s">
         <v>624</v>
       </c>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="F639" s="8"/>
     </row>
-    <row r="640" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="4" t="s">
         <v>625</v>
       </c>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="F640" s="8"/>
     </row>
-    <row r="641" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="4" t="s">
         <v>627</v>
       </c>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="F641" s="8"/>
     </row>
-    <row r="642" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="4" t="s">
         <v>628</v>
       </c>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="F642" s="8"/>
     </row>
-    <row r="643" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="4" t="s">
         <v>629</v>
       </c>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="F643" s="8"/>
     </row>
-    <row r="644" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="4" t="s">
         <v>630</v>
       </c>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="F644" s="8"/>
     </row>
-    <row r="645" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="4" t="s">
         <v>631</v>
       </c>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="F645" s="8"/>
     </row>
-    <row r="646" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="4" t="s">
         <v>632</v>
       </c>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F646" s="8"/>
     </row>
-    <row r="647" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="4" t="s">
         <v>633</v>
       </c>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="F647" s="8"/>
     </row>
-    <row r="648" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="4" t="s">
         <v>634</v>
       </c>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="F648" s="8"/>
     </row>
-    <row r="649" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="4" t="s">
         <v>635</v>
       </c>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="F649" s="8"/>
     </row>
-    <row r="650" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="4" t="s">
         <v>636</v>
       </c>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="F650" s="8"/>
     </row>
-    <row r="651" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="4" t="s">
         <v>637</v>
       </c>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="F651" s="8"/>
     </row>
-    <row r="652" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="4" t="s">
         <v>638</v>
       </c>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="F652" s="8"/>
     </row>
-    <row r="653" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="4" t="s">
         <v>639</v>
       </c>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="F653" s="8"/>
     </row>
-    <row r="654" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="4" t="s">
         <v>640</v>
       </c>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="F654" s="8"/>
     </row>
-    <row r="655" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="4" t="s">
         <v>641</v>
       </c>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="F655" s="8"/>
     </row>
-    <row r="656" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="4" t="s">
         <v>642</v>
       </c>
@@ -14996,7 +14996,7 @@
       </c>
       <c r="F656" s="8"/>
     </row>
-    <row r="657" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="4" t="s">
         <v>644</v>
       </c>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="F657" s="8"/>
     </row>
-    <row r="658" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="4" t="s">
         <v>645</v>
       </c>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="F658" s="8"/>
     </row>
-    <row r="659" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="4" t="s">
         <v>647</v>
       </c>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="F659" s="8"/>
     </row>
-    <row r="660" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="4" t="s">
         <v>633</v>
       </c>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="F660" s="8"/>
     </row>
-    <row r="661" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="4" t="s">
         <v>637</v>
       </c>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F661" s="8"/>
     </row>
-    <row r="662" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="4" t="s">
         <v>649</v>
       </c>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="F662" s="8"/>
     </row>
-    <row r="663" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="4" t="s">
         <v>650</v>
       </c>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="F663" s="8"/>
     </row>
-    <row r="664" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="4" t="s">
         <v>651</v>
       </c>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="F664" s="8"/>
     </row>
-    <row r="665" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="4" t="s">
         <v>652</v>
       </c>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="F665" s="8"/>
     </row>
-    <row r="666" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="4" t="s">
         <v>653</v>
       </c>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="F666" s="8"/>
     </row>
-    <row r="667" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="4" t="s">
         <v>654</v>
       </c>
@@ -15194,7 +15194,7 @@
       </c>
       <c r="F667" s="8"/>
     </row>
-    <row r="668" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="4" t="s">
         <v>655</v>
       </c>
@@ -15212,7 +15212,7 @@
       </c>
       <c r="F668" s="8"/>
     </row>
-    <row r="669" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="4" t="s">
         <v>656</v>
       </c>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="F669" s="8"/>
     </row>
-    <row r="670" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="4" t="s">
         <v>650</v>
       </c>
@@ -15248,7 +15248,7 @@
       </c>
       <c r="F670" s="8"/>
     </row>
-    <row r="671" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="4" t="s">
         <v>649</v>
       </c>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F671" s="8"/>
     </row>
-    <row r="672" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="4" t="s">
         <v>657</v>
       </c>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="F672" s="8"/>
     </row>
-    <row r="673" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="4" t="s">
         <v>651</v>
       </c>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="F673" s="8"/>
     </row>
-    <row r="674" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="4" t="s">
         <v>658</v>
       </c>
@@ -15320,7 +15320,7 @@
       </c>
       <c r="F674" s="8"/>
     </row>
-    <row r="675" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="4" t="s">
         <v>660</v>
       </c>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="F675" s="8"/>
     </row>
-    <row r="676" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="4" t="s">
         <v>661</v>
       </c>
@@ -15356,7 +15356,7 @@
       </c>
       <c r="F676" s="8"/>
     </row>
-    <row r="677" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="4" t="s">
         <v>662</v>
       </c>
@@ -15374,7 +15374,7 @@
       </c>
       <c r="F677" s="8"/>
     </row>
-    <row r="678" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="4" t="s">
         <v>663</v>
       </c>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="F678" s="8"/>
     </row>
-    <row r="679" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="4" t="s">
         <v>665</v>
       </c>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="F679" s="8"/>
     </row>
-    <row r="680" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="4" t="s">
         <v>666</v>
       </c>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="F680" s="8"/>
     </row>
-    <row r="681" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="4" t="s">
         <v>668</v>
       </c>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="F681" s="8"/>
     </row>
-    <row r="682" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="4" t="s">
         <v>669</v>
       </c>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="F682" s="8"/>
     </row>
-    <row r="683" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="4" t="s">
         <v>670</v>
       </c>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="F683" s="8"/>
     </row>
-    <row r="684" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="4" t="s">
         <v>671</v>
       </c>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="F684" s="8"/>
     </row>
-    <row r="685" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="4" t="s">
         <v>672</v>
       </c>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="F685" s="8"/>
     </row>
-    <row r="686" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="4" t="s">
         <v>674</v>
       </c>
@@ -15536,7 +15536,7 @@
       </c>
       <c r="F686" s="8"/>
     </row>
-    <row r="687" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="4" t="s">
         <v>676</v>
       </c>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="F687" s="8"/>
     </row>
-    <row r="688" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="4" t="s">
         <v>677</v>
       </c>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="F688" s="8"/>
     </row>
-    <row r="689" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="4" t="s">
         <v>678</v>
       </c>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="F689" s="8"/>
     </row>
-    <row r="690" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="4" t="s">
         <v>660</v>
       </c>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="F690" s="8"/>
     </row>
-    <row r="691" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="4" t="s">
         <v>680</v>
       </c>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="F691" s="8"/>
     </row>
-    <row r="692" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="4" t="s">
         <v>665</v>
       </c>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="F692" s="8"/>
     </row>
-    <row r="693" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="4" t="s">
         <v>682</v>
       </c>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="F693" s="8"/>
     </row>
-    <row r="694" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="4" t="s">
         <v>683</v>
       </c>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="F694" s="8"/>
     </row>
-    <row r="695" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="4" t="s">
         <v>684</v>
       </c>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="F695" s="8"/>
     </row>
-    <row r="696" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="4" t="s">
         <v>663</v>
       </c>
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F696" s="8"/>
     </row>
-    <row r="697" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="4" t="s">
         <v>685</v>
       </c>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="F697" s="8"/>
     </row>
-    <row r="698" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="4" t="s">
         <v>686</v>
       </c>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="F698" s="8"/>
     </row>
-    <row r="699" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="4" t="s">
         <v>687</v>
       </c>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="F699" s="8"/>
     </row>
-    <row r="700" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="4" t="s">
         <v>688</v>
       </c>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="F700" s="8"/>
     </row>
-    <row r="701" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="4" t="s">
         <v>690</v>
       </c>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="F701" s="8"/>
     </row>
-    <row r="702" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="4" t="s">
         <v>691</v>
       </c>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="F702" s="8"/>
     </row>
-    <row r="703" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="4" t="s">
         <v>692</v>
       </c>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="F703" s="8"/>
     </row>
-    <row r="704" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="4" t="s">
         <v>693</v>
       </c>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="F704" s="8"/>
     </row>
-    <row r="705" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="4" t="s">
         <v>694</v>
       </c>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="F705" s="8"/>
     </row>
-    <row r="706" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="4" t="s">
         <v>695</v>
       </c>
@@ -15896,7 +15896,7 @@
       </c>
       <c r="F706" s="8"/>
     </row>
-    <row r="707" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="4" t="s">
         <v>696</v>
       </c>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="F707" s="8"/>
     </row>
-    <row r="708" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="4" t="s">
         <v>697</v>
       </c>
@@ -15932,7 +15932,7 @@
       </c>
       <c r="F708" s="8"/>
     </row>
-    <row r="709" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="4" t="s">
         <v>698</v>
       </c>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="F709" s="8"/>
     </row>
-    <row r="710" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="4" t="s">
         <v>699</v>
       </c>
@@ -15968,7 +15968,7 @@
       </c>
       <c r="F710" s="8"/>
     </row>
-    <row r="711" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="4" t="s">
         <v>700</v>
       </c>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="F711" s="8"/>
     </row>
-    <row r="712" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="4" t="s">
         <v>701</v>
       </c>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="F712" s="8"/>
     </row>
-    <row r="713" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="4" t="s">
         <v>702</v>
       </c>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="F713" s="8"/>
     </row>
-    <row r="714" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="4" t="s">
         <v>703</v>
       </c>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="F714" s="8"/>
     </row>
-    <row r="715" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="4" t="s">
         <v>704</v>
       </c>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="F715" s="8"/>
     </row>
-    <row r="716" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="4" t="s">
         <v>705</v>
       </c>
@@ -16076,7 +16076,7 @@
       </c>
       <c r="F716" s="8"/>
     </row>
-    <row r="717" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="4" t="s">
         <v>706</v>
       </c>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="F717" s="8"/>
     </row>
-    <row r="718" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="4" t="s">
         <v>707</v>
       </c>
@@ -16112,7 +16112,7 @@
       </c>
       <c r="F718" s="8"/>
     </row>
-    <row r="719" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="4" t="s">
         <v>708</v>
       </c>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="F719" s="8"/>
     </row>
-    <row r="720" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="4" t="s">
         <v>709</v>
       </c>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="F720" s="8"/>
     </row>
-    <row r="721" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="4" t="s">
         <v>710</v>
       </c>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F721" s="8"/>
     </row>
-    <row r="722" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="4" t="s">
         <v>711</v>
       </c>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="F722" s="8"/>
     </row>
-    <row r="723" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="4" t="s">
         <v>712</v>
       </c>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="F723" s="8"/>
     </row>
-    <row r="724" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="4" t="s">
         <v>713</v>
       </c>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="F724" s="8"/>
     </row>
-    <row r="725" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="4" t="s">
         <v>714</v>
       </c>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="F725" s="8"/>
     </row>
-    <row r="726" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="4" t="s">
         <v>715</v>
       </c>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="F726" s="8"/>
     </row>
-    <row r="727" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="4" t="s">
         <v>716</v>
       </c>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="F727" s="8"/>
     </row>
-    <row r="728" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="4" t="s">
         <v>717</v>
       </c>
@@ -16292,7 +16292,7 @@
       </c>
       <c r="F728" s="8"/>
     </row>
-    <row r="729" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="4" t="s">
         <v>718</v>
       </c>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="F729" s="8"/>
     </row>
-    <row r="730" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="4" t="s">
         <v>719</v>
       </c>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="F730" s="8"/>
     </row>
-    <row r="731" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="4" t="s">
         <v>720</v>
       </c>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="F731" s="8"/>
     </row>
-    <row r="732" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="4" t="s">
         <v>721</v>
       </c>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="F732" s="8"/>
     </row>
-    <row r="733" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="4" t="s">
         <v>722</v>
       </c>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="F733" s="8"/>
     </row>
-    <row r="734" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="4" t="s">
         <v>723</v>
       </c>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="F734" s="8"/>
     </row>
-    <row r="735" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="4" t="s">
         <v>724</v>
       </c>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="F735" s="8"/>
     </row>
-    <row r="736" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="4" t="s">
         <v>725</v>
       </c>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="F736" s="8"/>
     </row>
-    <row r="737" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="4" t="s">
         <v>726</v>
       </c>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="F737" s="8"/>
     </row>
-    <row r="738" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="4" t="s">
         <v>727</v>
       </c>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="F738" s="8"/>
     </row>
-    <row r="739" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="4" t="s">
         <v>728</v>
       </c>
@@ -16490,7 +16490,7 @@
       </c>
       <c r="F739" s="8"/>
     </row>
-    <row r="740" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="4" t="s">
         <v>729</v>
       </c>
@@ -16508,7 +16508,7 @@
       </c>
       <c r="F740" s="8"/>
     </row>
-    <row r="741" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="4" t="s">
         <v>730</v>
       </c>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="F741" s="8"/>
     </row>
-    <row r="742" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="4" t="s">
         <v>731</v>
       </c>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="F742" s="8"/>
     </row>
-    <row r="743" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="4" t="s">
         <v>732</v>
       </c>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="F743" s="8"/>
     </row>
-    <row r="744" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="4" t="s">
         <v>733</v>
       </c>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="F744" s="8"/>
     </row>
-    <row r="745" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="4" t="s">
         <v>734</v>
       </c>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="F745" s="8"/>
     </row>
-    <row r="746" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="4" t="s">
         <v>735</v>
       </c>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F746" s="8"/>
     </row>
-    <row r="747" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="4" t="s">
         <v>737</v>
       </c>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="F747" s="8"/>
     </row>
-    <row r="748" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="4" t="s">
         <v>738</v>
       </c>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="F748" s="8"/>
     </row>
-    <row r="749" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="4" t="s">
         <v>739</v>
       </c>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="F749" s="8"/>
     </row>
-    <row r="750" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="4" t="s">
         <v>740</v>
       </c>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="F750" s="8"/>
     </row>
-    <row r="751" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="4" t="s">
         <v>741</v>
       </c>
@@ -16706,7 +16706,7 @@
       </c>
       <c r="F751" s="8"/>
     </row>
-    <row r="752" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="4" t="s">
         <v>742</v>
       </c>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="F752" s="8"/>
     </row>
-    <row r="753" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="4" t="s">
         <v>743</v>
       </c>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="F753" s="8"/>
     </row>
-    <row r="754" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="4" t="s">
         <v>744</v>
       </c>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="F754" s="8"/>
     </row>
-    <row r="755" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="4" t="s">
         <v>745</v>
       </c>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="F755" s="8"/>
     </row>
-    <row r="756" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="4" t="s">
         <v>746</v>
       </c>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="F756" s="8"/>
     </row>
-    <row r="757" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="4" t="s">
         <v>747</v>
       </c>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="F757" s="8"/>
     </row>
-    <row r="758" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="4" t="s">
         <v>748</v>
       </c>
@@ -16832,7 +16832,7 @@
       </c>
       <c r="F758" s="8"/>
     </row>
-    <row r="759" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="4" t="s">
         <v>749</v>
       </c>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="F759" s="8"/>
     </row>
-    <row r="760" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="4" t="s">
         <v>750</v>
       </c>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="F760" s="8"/>
     </row>
-    <row r="761" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="4" t="s">
         <v>751</v>
       </c>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="F761" s="8"/>
     </row>
-    <row r="762" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="4" t="s">
         <v>698</v>
       </c>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F762" s="8"/>
     </row>
-    <row r="763" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="4" t="s">
         <v>699</v>
       </c>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="F763" s="8"/>
     </row>
-    <row r="764" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="4" t="s">
         <v>700</v>
       </c>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="F764" s="8"/>
     </row>
-    <row r="765" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="4" t="s">
         <v>702</v>
       </c>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="F765" s="8"/>
     </row>
-    <row r="766" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="4" t="s">
         <v>701</v>
       </c>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="F766" s="8"/>
     </row>
-    <row r="767" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="4" t="s">
         <v>752</v>
       </c>
@@ -16994,7 +16994,7 @@
       </c>
       <c r="F767" s="8"/>
     </row>
-    <row r="768" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="4" t="s">
         <v>753</v>
       </c>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="F768" s="8"/>
     </row>
-    <row r="769" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="4" t="s">
         <v>704</v>
       </c>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="F769" s="8"/>
     </row>
-    <row r="770" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="4" t="s">
         <v>754</v>
       </c>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="F770" s="8"/>
     </row>
-    <row r="771" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="4" t="s">
         <v>696</v>
       </c>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="F771" s="8"/>
     </row>
-    <row r="772" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="4" t="s">
         <v>710</v>
       </c>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="F772" s="8"/>
     </row>
-    <row r="773" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="4" t="s">
         <v>755</v>
       </c>
@@ -17102,7 +17102,7 @@
       </c>
       <c r="F773" s="8"/>
     </row>
-    <row r="774" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="4" t="s">
         <v>756</v>
       </c>
@@ -17120,7 +17120,7 @@
       </c>
       <c r="F774" s="8"/>
     </row>
-    <row r="775" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="4" t="s">
         <v>718</v>
       </c>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="F775" s="8"/>
     </row>
-    <row r="776" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="4" t="s">
         <v>694</v>
       </c>
@@ -17156,7 +17156,7 @@
       </c>
       <c r="F776" s="8"/>
     </row>
-    <row r="777" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="4" t="s">
         <v>757</v>
       </c>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="F777" s="8"/>
     </row>
-    <row r="778" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="4" t="s">
         <v>715</v>
       </c>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="F778" s="8"/>
     </row>
-    <row r="779" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="4" t="s">
         <v>719</v>
       </c>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="F779" s="8"/>
     </row>
-    <row r="780" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="4" t="s">
         <v>758</v>
       </c>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="F780" s="8"/>
     </row>
-    <row r="781" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="4" t="s">
         <v>759</v>
       </c>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="F781" s="8"/>
     </row>
-    <row r="782" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="4" t="s">
         <v>760</v>
       </c>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="F782" s="8"/>
     </row>
-    <row r="783" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="4" t="s">
         <v>761</v>
       </c>
@@ -17282,7 +17282,7 @@
       </c>
       <c r="F783" s="8"/>
     </row>
-    <row r="784" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="4" t="s">
         <v>762</v>
       </c>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="F784" s="8"/>
     </row>
-    <row r="785" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="4" t="s">
         <v>712</v>
       </c>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="F785" s="8"/>
     </row>
-    <row r="786" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="4" t="s">
         <v>693</v>
       </c>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="F786" s="8"/>
     </row>
-    <row r="787" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="4" t="s">
         <v>763</v>
       </c>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="F787" s="8"/>
     </row>
-    <row r="788" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="4" t="s">
         <v>764</v>
       </c>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="F788" s="8"/>
     </row>
-    <row r="789" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="4" t="s">
         <v>765</v>
       </c>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="F789" s="8"/>
     </row>
-    <row r="790" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="4" t="s">
         <v>767</v>
       </c>
@@ -17408,7 +17408,7 @@
       </c>
       <c r="F790" s="8"/>
     </row>
-    <row r="791" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="4" t="s">
         <v>768</v>
       </c>
@@ -17426,7 +17426,7 @@
       </c>
       <c r="F791" s="8"/>
     </row>
-    <row r="792" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="4" t="s">
         <v>769</v>
       </c>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="F792" s="8"/>
     </row>
-    <row r="793" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="4" t="s">
         <v>770</v>
       </c>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="F793" s="8"/>
     </row>
-    <row r="794" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="4" t="s">
         <v>771</v>
       </c>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F794" s="8"/>
     </row>
-    <row r="795" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="4" t="s">
         <v>772</v>
       </c>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="F795" s="8"/>
     </row>
-    <row r="796" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="4" t="s">
         <v>773</v>
       </c>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F796" s="8"/>
     </row>
-    <row r="797" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="4" t="s">
         <v>774</v>
       </c>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="F797" s="8"/>
     </row>
-    <row r="798" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="4" t="s">
         <v>775</v>
       </c>
@@ -17552,7 +17552,7 @@
       </c>
       <c r="F798" s="8"/>
     </row>
-    <row r="799" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="4" t="s">
         <v>776</v>
       </c>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="F799" s="8"/>
     </row>
-    <row r="800" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="4" t="s">
         <v>777</v>
       </c>
@@ -17588,7 +17588,7 @@
       </c>
       <c r="F800" s="8"/>
     </row>
-    <row r="801" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="4" t="s">
         <v>740</v>
       </c>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="F801" s="8"/>
     </row>
-    <row r="802" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="4" t="s">
         <v>778</v>
       </c>
@@ -17624,7 +17624,7 @@
       </c>
       <c r="F802" s="8"/>
     </row>
-    <row r="803" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="4" t="s">
         <v>743</v>
       </c>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="F803" s="8"/>
     </row>
-    <row r="804" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="4" t="s">
         <v>780</v>
       </c>
@@ -17660,7 +17660,7 @@
       </c>
       <c r="F804" s="8"/>
     </row>
-    <row r="805" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="4" t="s">
         <v>782</v>
       </c>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="F805" s="8"/>
     </row>
-    <row r="806" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="4" t="s">
         <v>741</v>
       </c>
@@ -17696,7 +17696,7 @@
       </c>
       <c r="F806" s="8"/>
     </row>
-    <row r="807" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="4" t="s">
         <v>783</v>
       </c>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="F807" s="8"/>
     </row>
-    <row r="808" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="4" t="s">
         <v>747</v>
       </c>
@@ -17732,7 +17732,7 @@
       </c>
       <c r="F808" s="8"/>
     </row>
-    <row r="809" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="4" t="s">
         <v>748</v>
       </c>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="F809" s="8"/>
     </row>
-    <row r="810" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="4" t="s">
         <v>749</v>
       </c>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="F810" s="8"/>
     </row>
-    <row r="811" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="4" t="s">
         <v>750</v>
       </c>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="F811" s="8"/>
     </row>
-    <row r="812" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="4" t="s">
         <v>784</v>
       </c>
@@ -17804,7 +17804,7 @@
       </c>
       <c r="F812" s="8"/>
     </row>
-    <row r="813" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="4" t="s">
         <v>785</v>
       </c>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="F813" s="8"/>
     </row>
-    <row r="814" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="4" t="s">
         <v>786</v>
       </c>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="F814" s="8"/>
     </row>
-    <row r="815" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="4" t="s">
         <v>787</v>
       </c>
@@ -17858,7 +17858,7 @@
       </c>
       <c r="F815" s="8"/>
     </row>
-    <row r="816" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="4" t="s">
         <v>788</v>
       </c>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="F816" s="8"/>
     </row>
-    <row r="817" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="4" t="s">
         <v>789</v>
       </c>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="F817" s="8"/>
     </row>
-    <row r="818" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="4" t="s">
         <v>790</v>
       </c>
@@ -17912,7 +17912,7 @@
       </c>
       <c r="F818" s="8"/>
     </row>
-    <row r="819" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="4" t="s">
         <v>792</v>
       </c>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="F819" s="8"/>
     </row>
-    <row r="820" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="4" t="s">
         <v>793</v>
       </c>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="F820" s="8"/>
     </row>
-    <row r="821" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="4" t="s">
         <v>795</v>
       </c>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F821" s="8"/>
     </row>
-    <row r="822" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="4" t="s">
         <v>796</v>
       </c>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="F822" s="8"/>
     </row>
-    <row r="823" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="4" t="s">
         <v>797</v>
       </c>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="F823" s="8"/>
     </row>
-    <row r="824" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="4" t="s">
         <v>799</v>
       </c>
@@ -18020,7 +18020,7 @@
       </c>
       <c r="F824" s="8"/>
     </row>
-    <row r="825" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="4" t="s">
         <v>801</v>
       </c>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="F825" s="8"/>
     </row>
-    <row r="826" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="4" t="s">
         <v>802</v>
       </c>
@@ -18056,7 +18056,7 @@
       </c>
       <c r="F826" s="8"/>
     </row>
-    <row r="827" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="4" t="s">
         <v>803</v>
       </c>
@@ -18074,7 +18074,7 @@
       </c>
       <c r="F827" s="8"/>
     </row>
-    <row r="828" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="4" t="s">
         <v>805</v>
       </c>
@@ -18092,7 +18092,7 @@
       </c>
       <c r="F828" s="8"/>
     </row>
-    <row r="829" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="4" t="s">
         <v>806</v>
       </c>
@@ -18110,7 +18110,7 @@
       </c>
       <c r="F829" s="8"/>
     </row>
-    <row r="830" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="4" t="s">
         <v>807</v>
       </c>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="F830" s="8"/>
     </row>
-    <row r="831" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="4" t="s">
         <v>808</v>
       </c>
@@ -18146,7 +18146,7 @@
       </c>
       <c r="F831" s="8"/>
     </row>
-    <row r="832" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="4" t="s">
         <v>809</v>
       </c>
@@ -18164,7 +18164,7 @@
       </c>
       <c r="F832" s="8"/>
     </row>
-    <row r="833" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="4" t="s">
         <v>810</v>
       </c>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="F833" s="8"/>
     </row>
-    <row r="834" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="4" t="s">
         <v>811</v>
       </c>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="F834" s="8"/>
     </row>
-    <row r="835" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="4" t="s">
         <v>764</v>
       </c>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="F835" s="8"/>
     </row>
-    <row r="836" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="4" t="s">
         <v>763</v>
       </c>
@@ -18236,7 +18236,7 @@
       </c>
       <c r="F836" s="8"/>
     </row>
-    <row r="837" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="4" t="s">
         <v>812</v>
       </c>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="F837" s="8"/>
     </row>
-    <row r="838" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="4" t="s">
         <v>768</v>
       </c>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="F838" s="8"/>
     </row>
-    <row r="839" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="4" t="s">
         <v>813</v>
       </c>
@@ -18290,7 +18290,7 @@
       </c>
       <c r="F839" s="8"/>
     </row>
-    <row r="840" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="4" t="s">
         <v>814</v>
       </c>
@@ -18308,7 +18308,7 @@
       </c>
       <c r="F840" s="8"/>
     </row>
-    <row r="841" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="4" t="s">
         <v>816</v>
       </c>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="F841" s="8"/>
     </row>
-    <row r="842" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="4" t="s">
         <v>817</v>
       </c>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="F842" s="8"/>
     </row>
-    <row r="843" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="4" t="s">
         <v>774</v>
       </c>
@@ -18362,7 +18362,7 @@
       </c>
       <c r="F843" s="8"/>
     </row>
-    <row r="844" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="4" t="s">
         <v>773</v>
       </c>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="F844" s="8"/>
     </row>
-    <row r="845" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="4" t="s">
         <v>775</v>
       </c>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="F845" s="8"/>
     </row>
-    <row r="846" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="4" t="s">
         <v>740</v>
       </c>
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F846" s="8"/>
     </row>
-    <row r="847" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="4" t="s">
         <v>818</v>
       </c>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="F847" s="8"/>
     </row>
-    <row r="848" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="4" t="s">
         <v>819</v>
       </c>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="F848" s="8"/>
     </row>
-    <row r="849" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="4" t="s">
         <v>820</v>
       </c>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="F849" s="8"/>
     </row>
-    <row r="850" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="4" t="s">
         <v>822</v>
       </c>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="F850" s="8"/>
     </row>
-    <row r="851" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="4" t="s">
         <v>824</v>
       </c>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="F851" s="8"/>
     </row>
-    <row r="852" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="4" t="s">
         <v>825</v>
       </c>
@@ -18524,7 +18524,7 @@
       </c>
       <c r="F852" s="8"/>
     </row>
-    <row r="853" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="4" t="s">
         <v>826</v>
       </c>
@@ -18542,7 +18542,7 @@
       </c>
       <c r="F853" s="8"/>
     </row>
-    <row r="854" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="4" t="s">
         <v>827</v>
       </c>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="F854" s="8"/>
     </row>
-    <row r="855" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="4" t="s">
         <v>828</v>
       </c>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="F855" s="8"/>
     </row>
-    <row r="856" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="4" t="s">
         <v>829</v>
       </c>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="F856" s="8"/>
     </row>
-    <row r="857" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="4" t="s">
         <v>830</v>
       </c>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="F857" s="8"/>
     </row>
-    <row r="858" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="4" t="s">
         <v>831</v>
       </c>
@@ -18632,7 +18632,7 @@
       </c>
       <c r="F858" s="8"/>
     </row>
-    <row r="859" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="4" t="s">
         <v>832</v>
       </c>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="F859" s="8"/>
     </row>
-    <row r="860" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="4" t="s">
         <v>833</v>
       </c>
@@ -18668,7 +18668,7 @@
       </c>
       <c r="F860" s="8"/>
     </row>
-    <row r="861" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="4" t="s">
         <v>834</v>
       </c>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="F861" s="8"/>
     </row>
-    <row r="862" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="4" t="s">
         <v>835</v>
       </c>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="F862" s="8"/>
     </row>
-    <row r="863" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="4" t="s">
         <v>836</v>
       </c>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="F863" s="8"/>
     </row>
-    <row r="864" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="4" t="s">
         <v>838</v>
       </c>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="F864" s="8"/>
     </row>
-    <row r="865" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="4" t="s">
         <v>839</v>
       </c>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="F865" s="8"/>
     </row>
-    <row r="866" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="4" t="s">
         <v>840</v>
       </c>
@@ -18776,7 +18776,7 @@
       </c>
       <c r="F866" s="8"/>
     </row>
-    <row r="867" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="4" t="s">
         <v>841</v>
       </c>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="F867" s="8"/>
     </row>
-    <row r="868" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="4" t="s">
         <v>842</v>
       </c>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="F868" s="8"/>
     </row>
-    <row r="869" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="4" t="s">
         <v>843</v>
       </c>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="F869" s="8"/>
     </row>
-    <row r="870" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="4" t="s">
         <v>844</v>
       </c>
@@ -18848,7 +18848,7 @@
       </c>
       <c r="F870" s="8"/>
     </row>
-    <row r="871" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="4" t="s">
         <v>845</v>
       </c>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F871" s="8"/>
     </row>
-    <row r="872" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="4" t="s">
         <v>846</v>
       </c>
@@ -18884,7 +18884,7 @@
       </c>
       <c r="F872" s="8"/>
     </row>
-    <row r="873" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="4" t="s">
         <v>847</v>
       </c>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="F873" s="8"/>
     </row>
-    <row r="874" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="4" t="s">
         <v>848</v>
       </c>
@@ -18920,7 +18920,7 @@
       </c>
       <c r="F874" s="8"/>
     </row>
-    <row r="875" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="4" t="s">
         <v>849</v>
       </c>
@@ -18938,7 +18938,7 @@
       </c>
       <c r="F875" s="8"/>
     </row>
-    <row r="876" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="4" t="s">
         <v>850</v>
       </c>
@@ -18956,7 +18956,7 @@
       </c>
       <c r="F876" s="8"/>
     </row>
-    <row r="877" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="4" t="s">
         <v>851</v>
       </c>
@@ -18974,7 +18974,7 @@
       </c>
       <c r="F877" s="8"/>
     </row>
-    <row r="878" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="4" t="s">
         <v>852</v>
       </c>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="F878" s="8"/>
     </row>
-    <row r="879" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="4" t="s">
         <v>853</v>
       </c>
@@ -19010,7 +19010,7 @@
       </c>
       <c r="F879" s="8"/>
     </row>
-    <row r="880" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="4" t="s">
         <v>854</v>
       </c>
@@ -19028,7 +19028,7 @@
       </c>
       <c r="F880" s="8"/>
     </row>
-    <row r="881" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="4" t="s">
         <v>855</v>
       </c>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="F881" s="8"/>
     </row>
-    <row r="882" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="4" t="s">
         <v>856</v>
       </c>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="F882" s="8"/>
     </row>
-    <row r="883" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="4" t="s">
         <v>857</v>
       </c>
@@ -19082,7 +19082,7 @@
       </c>
       <c r="F883" s="8"/>
     </row>
-    <row r="884" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="4" t="s">
         <v>835</v>
       </c>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="F884" s="8"/>
     </row>
-    <row r="885" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:6" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="5" t="s">
         <v>858</v>
       </c>
@@ -19120,7 +19120,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="886" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="4" t="s">
         <v>842</v>
       </c>
@@ -19138,7 +19138,7 @@
       </c>
       <c r="F886" s="8"/>
     </row>
-    <row r="887" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="4" t="s">
         <v>839</v>
       </c>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="F887" s="8"/>
     </row>
-    <row r="888" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="4" t="s">
         <v>841</v>
       </c>
@@ -19174,7 +19174,7 @@
       </c>
       <c r="F888" s="8"/>
     </row>
-    <row r="889" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="4" t="s">
         <v>840</v>
       </c>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="F889" s="8"/>
     </row>
-    <row r="890" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="4" t="s">
         <v>838</v>
       </c>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="F890" s="8"/>
     </row>
-    <row r="891" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="4" t="s">
         <v>843</v>
       </c>
@@ -19228,7 +19228,7 @@
       </c>
       <c r="F891" s="8"/>
     </row>
-    <row r="892" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="4" t="s">
         <v>859</v>
       </c>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="F892" s="8"/>
     </row>
-    <row r="893" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="4" t="s">
         <v>845</v>
       </c>
@@ -19264,7 +19264,7 @@
       </c>
       <c r="F893" s="8"/>
     </row>
-    <row r="894" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="4" t="s">
         <v>846</v>
       </c>
@@ -19282,7 +19282,7 @@
       </c>
       <c r="F894" s="8"/>
     </row>
-    <row r="895" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="4" t="s">
         <v>844</v>
       </c>
@@ -19300,7 +19300,7 @@
       </c>
       <c r="F895" s="8"/>
     </row>
-    <row r="896" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="4" t="s">
         <v>860</v>
       </c>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="F896" s="8"/>
     </row>
-    <row r="897" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="4" t="s">
         <v>861</v>
       </c>
@@ -19336,7 +19336,7 @@
       </c>
       <c r="F897" s="8"/>
     </row>
-    <row r="898" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="4" t="s">
         <v>862</v>
       </c>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F898" s="8"/>
     </row>
-    <row r="899" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="4" t="s">
         <v>863</v>
       </c>
@@ -19372,7 +19372,7 @@
       </c>
       <c r="F899" s="8"/>
     </row>
-    <row r="900" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="4" t="s">
         <v>864</v>
       </c>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="F900" s="8"/>
     </row>
-    <row r="901" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="4" t="s">
         <v>865</v>
       </c>
@@ -19408,7 +19408,7 @@
       </c>
       <c r="F901" s="8"/>
     </row>
-    <row r="902" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="4" t="s">
         <v>866</v>
       </c>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="F902" s="8"/>
     </row>
-    <row r="903" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="4" t="s">
         <v>867</v>
       </c>
@@ -19444,7 +19444,7 @@
       </c>
       <c r="F903" s="8"/>
     </row>
-    <row r="904" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="4" t="s">
         <v>868</v>
       </c>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="F904" s="8"/>
     </row>
-    <row r="905" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="4" t="s">
         <v>869</v>
       </c>
@@ -19480,7 +19480,7 @@
       </c>
       <c r="F905" s="8"/>
     </row>
-    <row r="906" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="4" t="s">
         <v>870</v>
       </c>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="F906" s="8"/>
     </row>
-    <row r="907" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="4" t="s">
         <v>871</v>
       </c>
@@ -19516,7 +19516,7 @@
       </c>
       <c r="F907" s="8"/>
     </row>
-    <row r="908" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="4" t="s">
         <v>872</v>
       </c>
@@ -19534,7 +19534,7 @@
       </c>
       <c r="F908" s="8"/>
     </row>
-    <row r="909" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="4" t="s">
         <v>852</v>
       </c>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="F909" s="8"/>
     </row>
-    <row r="910" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="4" t="s">
         <v>851</v>
       </c>
@@ -19570,7 +19570,7 @@
       </c>
       <c r="F910" s="8"/>
     </row>
-    <row r="911" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="4" t="s">
         <v>857</v>
       </c>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="F911" s="8"/>
     </row>
-    <row r="912" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="4" t="s">
         <v>873</v>
       </c>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="F912" s="8"/>
     </row>
-    <row r="913" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="4" t="s">
         <v>874</v>
       </c>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="F913" s="8"/>
     </row>
-    <row r="914" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="4" t="s">
         <v>876</v>
       </c>
@@ -19642,7 +19642,7 @@
       </c>
       <c r="F914" s="8"/>
     </row>
-    <row r="915" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="4" t="s">
         <v>877</v>
       </c>
@@ -19660,7 +19660,7 @@
       </c>
       <c r="F915" s="8"/>
     </row>
-    <row r="916" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="4" t="s">
         <v>879</v>
       </c>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="F916" s="8"/>
     </row>
-    <row r="917" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="4" t="s">
         <v>880</v>
       </c>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="F917" s="8"/>
     </row>
-    <row r="918" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="4" t="s">
         <v>881</v>
       </c>
@@ -19714,7 +19714,7 @@
       </c>
       <c r="F918" s="8"/>
     </row>
-    <row r="919" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="4" t="s">
         <v>862</v>
       </c>
@@ -19732,7 +19732,7 @@
       </c>
       <c r="F919" s="8"/>
     </row>
-    <row r="920" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="4" t="s">
         <v>861</v>
       </c>
@@ -19750,7 +19750,7 @@
       </c>
       <c r="F920" s="8"/>
     </row>
-    <row r="921" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="4" t="s">
         <v>860</v>
       </c>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F921" s="8"/>
     </row>
-    <row r="922" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="4" t="s">
         <v>868</v>
       </c>
@@ -19786,7 +19786,7 @@
       </c>
       <c r="F922" s="8"/>
     </row>
-    <row r="923" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="4" t="s">
         <v>867</v>
       </c>
@@ -19804,7 +19804,7 @@
       </c>
       <c r="F923" s="8"/>
     </row>
-    <row r="924" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="4" t="s">
         <v>866</v>
       </c>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="F924" s="8"/>
     </row>
-    <row r="925" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="4" t="s">
         <v>882</v>
       </c>
@@ -19840,7 +19840,7 @@
       </c>
       <c r="F925" s="8"/>
     </row>
-    <row r="926" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="4" t="s">
         <v>883</v>
       </c>
@@ -19858,7 +19858,7 @@
       </c>
       <c r="F926" s="8"/>
     </row>
-    <row r="927" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="4" t="s">
         <v>884</v>
       </c>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="F927" s="8"/>
     </row>
-    <row r="928" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="4" t="s">
         <v>865</v>
       </c>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="F928" s="8"/>
     </row>
-    <row r="929" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="4" t="s">
         <v>869</v>
       </c>
@@ -19912,7 +19912,7 @@
       </c>
       <c r="F929" s="8"/>
     </row>
-    <row r="930" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="4" t="s">
         <v>886</v>
       </c>
@@ -19930,7 +19930,7 @@
       </c>
       <c r="F930" s="8"/>
     </row>
-    <row r="931" spans="1:6" ht="33.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:6" ht="33.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="4" t="s">
         <v>887</v>
       </c>
@@ -19948,7 +19948,7 @@
       </c>
       <c r="F931" s="8"/>
     </row>
-    <row r="934" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A934">
         <v>1</v>
       </c>
@@ -19956,7 +19956,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="935" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A935">
         <v>2</v>
       </c>
@@ -19964,7 +19964,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="936" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A936">
         <v>3</v>
       </c>
@@ -19975,7 +19975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="937" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A937">
         <v>4</v>
       </c>
@@ -20005,13 +20005,13 @@
     <tabColor theme="6"/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="3" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20028,7 +20028,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>891</v>
       </c>
@@ -20045,7 +20045,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
